--- a/CNTR_AT_2020.xlsx
+++ b/CNTR_AT_2020.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfcbs.warnier\Work Folders\Documents\Resilience dashboard project\ref-countries-2020-60m.geojson\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="c:\Users\jfcbs.warnier\Work Folders\Documents\Resilience dashboard project\ref-countries-2020-60m.geojson\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -27,6 +27,30 @@
     <author>JFCBS PLANS J9 CIMIC PPO WARNIER Axel OF-3</author>
   </authors>
   <commentList>
+    <comment ref="G14" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>JFCBS PLANS J9 CIMIC PPO WARNIER Axel OF-3:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+polygon closed but on the western border 1 line goes inwards</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="G74" authorId="0" shapeId="0">
       <text>
         <r>
@@ -56,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1227" uniqueCount="976">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1231" uniqueCount="979">
   <si>
     <t>CNTR_ID</t>
   </si>
@@ -2971,9 +2995,6 @@
     <t>Y</t>
   </si>
   <si>
-    <t>Polygon_Ready</t>
-  </si>
-  <si>
     <t>N</t>
   </si>
   <si>
@@ -2984,6 +3005,18 @@
   </si>
   <si>
     <t>1051, 1043, 1031, 1009, 1312</t>
+  </si>
+  <si>
+    <t>999, 1000, 998, 1005, 1323</t>
+  </si>
+  <si>
+    <t>Rows to add</t>
+  </si>
+  <si>
+    <t>Rows to delete</t>
+  </si>
+  <si>
+    <t>64, 86, 113, 175, 391, 404, 433, 506</t>
   </si>
 </sst>
 </file>
@@ -3818,7 +3851,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G241"/>
+  <dimension ref="A1:H241"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="50.7109375" bestFit="1" customWidth="1"/>
@@ -3826,9 +3859,10 @@
     <col min="4" max="4" width="31.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="22.28515625" customWidth="1"/>
     <col min="7" max="7" width="25.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="30.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3848,10 +3882,13 @@
         <v>969</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>971</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+        <v>976</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -3868,7 +3905,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -3885,7 +3922,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -3902,7 +3939,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -3919,7 +3956,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -3936,7 +3973,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>28</v>
       </c>
@@ -3956,10 +3993,10 @@
         <v>970</v>
       </c>
       <c r="G7" t="s">
-        <v>972</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>32</v>
       </c>
@@ -3976,7 +4013,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>36</v>
       </c>
@@ -3993,7 +4030,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>41</v>
       </c>
@@ -4010,7 +4047,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>45</v>
       </c>
@@ -4024,7 +4061,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>49</v>
       </c>
@@ -4041,7 +4078,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>53</v>
       </c>
@@ -4058,30 +4095,31 @@
         <v>57</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D14" t="s">
-        <v>9</v>
-      </c>
-      <c r="E14" t="s">
+      <c r="D14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F14" s="3" t="s">
         <v>970</v>
       </c>
-      <c r="G14" t="s">
-        <v>972</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G14" s="3" t="s">
+        <v>975</v>
+      </c>
+      <c r="H14" s="3"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>62</v>
       </c>
@@ -4098,7 +4136,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>66</v>
       </c>
@@ -4152,7 +4190,7 @@
         <v>970</v>
       </c>
       <c r="G18" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -4249,7 +4287,7 @@
         <v>970</v>
       </c>
       <c r="G23" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -4567,7 +4605,7 @@
         <v>970</v>
       </c>
       <c r="G41" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -4794,7 +4832,7 @@
         <v>970</v>
       </c>
       <c r="G54" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -4967,7 +5005,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>264</v>
       </c>
@@ -4984,7 +5022,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>268</v>
       </c>
@@ -5001,7 +5039,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>272</v>
       </c>
@@ -5021,10 +5059,10 @@
         <v>970</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>974</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>276</v>
       </c>
@@ -5041,7 +5079,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>280</v>
       </c>
@@ -5058,7 +5096,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>284</v>
       </c>
@@ -5075,7 +5113,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>288</v>
       </c>
@@ -5092,7 +5130,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>293</v>
       </c>
@@ -5109,7 +5147,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>297</v>
       </c>
@@ -5126,7 +5164,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
         <v>302</v>
       </c>
@@ -5142,12 +5180,17 @@
       <c r="E74" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="F74" s="3"/>
+      <c r="F74" s="3" t="s">
+        <v>970</v>
+      </c>
       <c r="G74" s="3" t="s">
-        <v>975</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+        <v>974</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>306</v>
       </c>
@@ -5164,7 +5207,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>312</v>
       </c>
@@ -5181,7 +5224,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>316</v>
       </c>
@@ -5198,7 +5241,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>320</v>
       </c>
@@ -5215,7 +5258,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>324</v>
       </c>
@@ -5232,7 +5275,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>329</v>
       </c>
@@ -5521,7 +5564,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>393</v>
       </c>
@@ -5538,7 +5581,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>397</v>
       </c>
@@ -5555,7 +5598,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>401</v>
       </c>
@@ -5572,7 +5615,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>405</v>
       </c>
@@ -5589,7 +5632,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>410</v>
       </c>
@@ -5606,7 +5649,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>414</v>
       </c>
@@ -5623,7 +5666,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>418</v>
       </c>
@@ -5640,7 +5683,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>422</v>
       </c>
@@ -5657,24 +5700,30 @@
         <v>425</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A105" s="2" t="s">
         <v>426</v>
       </c>
-      <c r="B105" t="s">
+      <c r="B105" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="C105" t="s">
+      <c r="C105" s="2" t="s">
         <v>428</v>
       </c>
-      <c r="D105" t="s">
-        <v>9</v>
-      </c>
-      <c r="E105" t="s">
+      <c r="D105" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E105" s="2" t="s">
         <v>429</v>
       </c>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F105" s="2" t="s">
+        <v>970</v>
+      </c>
+      <c r="G105" s="2">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>431</v>
       </c>
@@ -5691,7 +5740,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>435</v>
       </c>
@@ -5708,7 +5757,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>438</v>
       </c>
@@ -5725,7 +5774,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>442</v>
       </c>
@@ -5742,7 +5791,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>446</v>
       </c>
@@ -5759,7 +5808,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>450</v>
       </c>
@@ -5776,7 +5825,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>454</v>
       </c>

--- a/CNTR_AT_2020.xlsx
+++ b/CNTR_AT_2020.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25200" windowHeight="11850"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="19425" windowHeight="11025"/>
   </bookViews>
   <sheets>
     <sheet name="CNTR_AT_2020" sheetId="1" r:id="rId1"/>
@@ -51,6 +51,30 @@
         </r>
       </text>
     </comment>
+    <comment ref="G23" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>JFCBS PLANS J9 CIMIC PPO WARNIER Axel OF-3:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Not completed. Waiting for borders GRC</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="G74" authorId="0" shapeId="0">
       <text>
         <r>
@@ -80,7 +104,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1231" uniqueCount="979">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1370" uniqueCount="1032">
   <si>
     <t>CNTR_ID</t>
   </si>
@@ -1357,9 +1381,6 @@
     <t>ISL</t>
   </si>
   <si>
-    <t>ReykjavÃ­k</t>
-  </si>
-  <si>
     <t>IT</t>
   </si>
   <si>
@@ -2704,9 +2725,6 @@
     <t>TR</t>
   </si>
   <si>
-    <t>TÃ¼rkiye</t>
-  </si>
-  <si>
     <t>TUR</t>
   </si>
   <si>
@@ -3017,6 +3035,171 @@
   </si>
   <si>
     <t>64, 86, 113, 175, 391, 404, 433, 506</t>
+  </si>
+  <si>
+    <t>Polygons</t>
+  </si>
+  <si>
+    <t>MULTIPOLYGON (((4479217.802100001 1536458.3197000008, 4487649.129000001 1545685.8505000006, 4518351.7531 1531189.0841000006, 4500970.6493 1507150.235200001, 4479217.802100001 1536458.3197000008)), ((4792129.5252 1692431.0241, 4787071.7480999995 1652570.0656000003, 4775275.4198 1602135.1038000006, 4791105.577099999 1571965.6993000004, 4771337.8016 1529624.4864000008, 4732533.237299999 1534570.0101999994, 4710072.1544 1558882.7113000005, 4682530.865 1568851.5188999996, 4578759.5769 1616090.8729999997, 4556151.842800001 1622071.7694000006, 4546803.6982 1653886.3219000008, 4584163.2787 1667359.9342999998, 4605538.501700001 1685110.6470999997, 4690793.236400001 1670054.6800999995, 4792129.5252 1692431.0241)), ((4178712.0921 1777247.9694999997, 4181881.6336000003 1818822.1631000005, 4191866.005000001 1848044.9605, 4189784.4738999996 1901712.7294999994, 4184513.1996999998 1924933.2226, 4171082.5823 1968064.5196000002, 4219713.067500001 1982154.6537999995, 4268806.916999999 2010861.2415999994, 4299705.048900001 1951216.7446999997, 4289165.4836 1900466.4927999992, 4290842.2005 1828771.5175, 4279335.9318 1788230.9803, 4199979.8377 1764520.0514000002, 4178712.0921 1777247.9694999997)), ((4510728.830499999 2621660.5086000003, 4527096.498 2619689.6187999994, 4530306.198799999 2617285.803200001, 4589828.600299999 2612229.3573000003, 4606152.070499999 2608175.0654000007, 4604291.080700001 2598604.5420999993, 4591448.658299999 2588075.378900001, 4591854.307499999 2555074.1741000004, 4600801.203500001 2529734.6720000003, 4600790.590299999 2528446.5233999994, 4615786.936899999 2521947.978599999, 4625607.4045 2510559.301999999, 4620627.842700001 2504937.5133999996, 4611706.6953 2505312.588199999, 4599618.362199999 2526057.5034999996, 4589953.6570999995 2516385.7314, 4582187.4428 2519520.6866999995, 4562837.831700001 2508581.9823000003, 4495895.107000001 2470763.3575999998, 4504513.282 2452710.476399999, 4511151.919199999 2412079.661699999, 4501438.159399999 2393730.2409000006, 4511885.271199999 2349087.2687999997, 4517387.1285999995 2342327.0321999993, 4542187.0638999995 2321829.948999999, 4577064.4146 2298875.7301000003, 4616324.151799999 2270013.7672000006, 4625430.5031 2250490.1938000005, 4625722.103499999 2249913.0874000005, 4626261.070699999 2248710.5479000006, 4626751.0372 2247578.164999999, 4627358.160700001 2246295.7541000005, 4627653.820599999 2245720.5506999996, 4628254.921399999 2244616.3332, 4628557.6581999995 2244104.8248999994, 4629807.9614 2240146.7781000007, 4631030.1565000005 2237181.0087, 4631633.512 2236265.9746000003, 4632308.327400001 2234298.9564999994, 4633316.567399999 2232322.4278999995, 4634480.054500001 2229759.138800001, 4634827.8828 2228807.7578, 4634997.6483 2227229.4637, 4635294.2158 2225749.9496, 4641630.086300001 2206987.3696999997, 4650921.624600001 2184702.9782999996, 4662614.362400001 2167738.8082, 4671923.4134 2158742.1172, 4717676.632300001 2119915.694700001, 4748383.586999999 2106070.6742000002, 4824160.8003 2109316.9856000002, 4824850.307600001 2090224.0295000002, 4826062.3496 2056175.3235999998, 4871066.9235 2038145.4593000002, 4945371.7378 2007500.8091000002, 4990654.573999999 1988739.8658000007, 5009076.984999999 1972177.3040999994, 5041303.092499999 1938834.7643, 5035626.410499999 1904443.9593000002, 5015703.3989 1908573.7260999996, 4983093.549900001 1945002.7710999995, 4905972.885 1948907.3000000007, 4889506.1939 1916502.2782000005, 4884047.857100001 1871924.1488000005, 4927897.3654 1849464.5260000005, 4939271.283299999 1802361.0481000002, 4921369.322899999 1787169.8807999995, 4909332.9245 1781128.2804000005, 4895575.9034 1760870.2741999999, 4898485.7995 1734482.4820000008, 4836966.787599999 1669863.5932999998, 4819543.7479 1691928.8340000007, 4840158.866 1733790.2212000005, 4863490.236500001 1769259.0022, 4851084.487400001 1794642.0122999996, 4815169.1022 1888734.5168999992, 4804763.6351 1901170.2929999996, 4756714.554 1912831.8747000005, 4727078.128900001 1954206.9710000008, 4701598.084799999 1960713.5135999992, 4662108.0463 1986871.4190999996, 4637532.455600001 2021521.166099999, 4553745.958900001 2039279.2923000008, 4513774.3632 2073011.7046000008, 4464782.959000001 2118743.7467, 4440807.365599999 2142554.3783, 4378764.8838 2204150.202299999, 4345279.331499999 2274842.6735999994, 4341816.6175999995 2300678.1303000003, 4332538.923900001 2318419.5977999996, 4322507.7072 2326070.842700001, 4281865.553300001 2345283.3445999995, 4211842.227299999 2364240.6691999994, 4170959.8007999994 2316230.6527999993, 4121719.5385 2300472.5979999993, 4137476.9604 2330752.1697000004, 4072437.7837000005 2366359.4788000006, 4078566.3036 2398682.6088999994, 4088123.4881999996 2404818.9069, 4055455.9967 2450215.5264, 4095551.4164000005 2465999.3100000005, 4094309.3320000004 2488413.1999999993, 4072064.4948999994 2523773.4279999994, 4091539.9584999997 2538951.4132000003, 4155107.7885999996 2536147.715, 4156152.8649000004 2537251.1045999993, 4196776.6841 2594561.0877, 4221436.720000001 2554668.332800001, 4236365.010399999 2524805.7344000004, 4256006.521 2562205.0749999993, 4262968.432399999 2569255.1774000004, 4270832.195599999 2595632.4387, 4324907.0221 2580200.1414, 4334343.9449000005 2607397.545600001, 4355774.3639 2602036.5163000003, 4356848.7469999995 2638051.4913, 4395997.266100001 2633155.3092, 4409680.1316 2650942.1194, 4444821.7107 2656889.1414, 4462343.119100001 2656248.4411999993, 4483320.7127 2665352.2216, 4491314.129799999 2664310.289000001, 4489656.706700001 2645101.3159, 4510728.830499999 2621660.5086000003)))</t>
+  </si>
+  <si>
+    <t>POLYGON ((2777974.267000001 1743031.7994, 2716789.8863999993 1743703.9405000005, 2650902.5336000007 1770068.8133000005, 2663467.4574999996 1801241.7698, 2669849.727600001 1828253.6971000005, 2694644.1553000007 1915721.6198999994, 2656160.146299999 1919937.5013999995, 2640740.7589 1957901.7792000007, 2650545.8937999997 1988702.1366000008, 2699298.2816000003 2054638.7631, 2718974.6217 2084386.7928999998, 2740605.9649 2132542.3486, 2761836.7282 2178696.657299999, 2764565.4979 2236104.0847999994, 2765263.257099999 2251928.6169000007, 2767741.0801 2281168.122199999, 2828168.7161 2298249.038899999, 2822605.4909000006 2261163.0436000004, 2831796.0873000007 2259162.0669, 2901984.571900001 2249097.1273999996, 2921462.8126999997 2255028.6382999998, 2947976.512700001 2240662.4060999993, 2968508.660700001 2201289.1238, 2947304.8771 2172124.7914000005, 2928114.7364000008 2166294.6163, 2904457.601 2151677.7938, 2903686.877800001 2094913.7258000001, 2892686.5370000005 2068076.5185000002, 2885229.647399999 2068270.8232000005, 2868562.2829 2012858.7808999997, 2822316.5429 2015259.6797000002, 2839691.3215999994 1967475.0245999992, 2851525.2676 1934571.5063000005, 2830219.0867999997 1909755.1043999996, 2817367.6576000005 1878991.0332999993, 2825810.8137 1846890.8708999995, 2841367.7413999997 1845643.4425000008, 2785763.5819000006 1800101.8616000004, 2776212.4310999997 1783297.5351, 2777974.267000001 1743031.7994))</t>
+  </si>
+  <si>
+    <t>POLYGON ((4044953.8672 3009232.5731000006, 4037218.2765999995 3015531.6271, 4015259.6960000005 2980087.2218999993, 4018497.2259 2945664.4036, 4012456.508300001 2945942.9268999994, 3993083.8806999996 2941704.5809000004, 3988312.6208999995 2955361.1799, 3971752.4340000004 2967666.1932999995, 3959123.5232999995 2977871.6417999994, 3949129.2158000004 3017066.643100001, 3921742.4297 2996168.7018, 3907618.9147999994 2999071.3099000007, 3901203.5385999996 3001917.1602, 3896518.9996000007 3044671.3225, 3876165.7367000002 3046342.8936, 3871119.5032 3058361.0966, 3868536.232000001 3061788.467599999, 3853161.5405 3069289.1185, 3844678.012599999 3088813.8804, 3835046.9453999996 3097095.6535, 3829391.7752 3097020.708799999, 3829124.514799999 3097051.1959000006, 3828830.3148999996 3096701.8082, 3828413.9506 3096281.0318, 3826732.1295 3095446.3819999993, 3825882.0142 3094749.912900001, 3825314.076199999 3094776.3259999994, 3824816.5967999995 3095157.707699999, 3823576.295499999 3094429.0299999993, 3823373.370100001 3093872.069700001, 3823719.6410000008 3092926.2487000003, 3823205.976399999 3092752.3683, 3822702.193499999 3092377.1894000005, 3822511.539000001 3090764.4552999996, 3821872.7488 3089834.652899999, 3821127.0906000007 3089941.3904, 3820865.0940000005 3089001.2928, 3820232.0768999998 3088929.274599999, 3819380.580499999 3090402.751, 3818208.9650999997 3090203.6359, 3817784.9420999996 3090853.9849999994, 3802065.476500001 3115282.907400001, 3799789.3935000002 3135288.8575, 3814726.499399999 3141880.0538, 3841458.8935000002 3156115.8939999994, 3859737.4079 3160854.8641999997, 3859809.09 3150168.8783, 3892268.487299999 3140257.5569, 3900841.3057000004 3141114.0470000003, 3919814.3946 3153328.4564999994, 3920366.332800001 3153922.6905000005, 3920660.2127 3156217.704, 3923161.9311999995 3156164.4332, 3950633.7397000007 3159702.9375, 3957506.818499999 3167694.4761999995, 3980658.9135 3157888.2239999995, 3988851.4396 3138673.9134, 4011459.8396000005 3132703.4902999997, 4026610.5578000005 3113861.8872999996, 4024033.4265 3108310.8542, 4017252.1834999993 3086772.5351, 4025883.6818000004 3075418.9510999992, 4040360.1849000007 3079039.3890000004, 4059686.3597 3049366.0593999997, 4065087.3355 3029745.6953, 4044953.8672 3009232.5731000006))</t>
+  </si>
+  <si>
+    <t>POLYGON ((4285464.4256 2684223.103700001, 4287756.7698 2714352.1854, 4318575.4584 2714736.6659999993, 4320964.2509 2707711.6807000004, 4334506.5766 2684074.9562, 4352656.717800001 2697259.9672999997, 4355225.3652 2715902.9925999995, 4387765.814200001 2714092.2085999995, 4395879.224099999 2698559.6253999993, 4397789.8456999995 2698611.856899999, 4428275.4441 2704501.090399999, 4427326.055500001 2710091.6841, 4443880.2947 2721225.526799999, 4460729.270300001 2722685.2793000005, 4475984.664100001 2724949.8110000007, 4496572.345000001 2734271.410700001, 4514603.5298 2727668.8101000004, 4523482.837200001 2733534.5822, 4550492.988700001 2716598.8374000005, 4542424.854499999 2755742.9772999994, 4535816.2831 2765181.807, 4534508.8895 2768916.1735999994, 4525936.166999999 2781511.587099999, 4539906.565199999 2792493.4747, 4556759.177300001 2802949.1988999993, 4576129.709899999 2833244.352, 4576657.3144000005 2832784.0842000004, 4577520.554300001 2832996.6304, 4577590.199999999 2833819.306399999, 4578256.6741 2833743.7687999997, 4578694.752699999 2834033.946799999, 4578831.8160999995 2834529.6916000005, 4579577.8562 2834988.9930000007, 4579714.7586 2835384.8275000006, 4579445.3671 2836171.4388999995, 4579671.3643 2836835.5207, 4579900.4079 2836889.7173999995, 4596341.521500001 2829133.7541000005, 4600312.774800001 2851666.636, 4603174.0754 2858273.119000001, 4666960.763 2841107.5930000003, 4689833.4824 2885245.5896000005, 4726983.6402 2881333.1931999996, 4742889.3682 2876362.7248, 4832035.225400001 2857836.831599999, 4833565.827299999 2848880.935799999, 4827291.811899999 2837437.805400001, 4839232.970000001 2808802.6084000003, 4846489.8573 2803511.3914, 4854633.2936 2791782.4586999994, 4844980.647700001 2758836.3794, 4802912.6987 2748897.5074000005, 4821838.7709 2726165.9716, 4806751.430600001 2714374.6019, 4811576.9648 2680342.3698999994, 4786947.8336 2658724.9250000007, 4778298.5133 2654263.0853000004, 4763403.3181 2638817.9725, 4753009.4882 2637824.3693000004, 4734492.067299999 2630626.1513, 4708765.1296999995 2628648.7771000005, 4680269.760500001 2604354.046, 4672386.9882 2595156.8956000004, 4661893.2820999995 2602363.9946, 4606152.070499999 2608175.0654000007, 4589828.600299999 2612229.3573000003, 4530306.198799999 2617285.803200001, 4527096.498 2619689.6187999994, 4510728.830499999 2621660.5086000003, 4489656.706700001 2645101.3159, 4491314.129799999 2664310.289000001, 4483320.7127 2665352.2216, 4462343.119100001 2656248.4411999993, 4444821.7107 2656889.1414, 4409680.1316 2650942.1194, 4395997.266100001 2633155.3092, 4356848.7469999995 2638051.4913, 4332066.8737 2637515.7503999993, 4291125.0428 2660883.3062999994, 4281155.7798 2659947.7641000003, 4285464.4256 2684223.103700001))</t>
+  </si>
+  <si>
+    <t>Row to correct</t>
+  </si>
+  <si>
+    <t>LINESTRING (2938041.8399 1592776.9705999997, 2935429.5359000005 1593682.6921999995, 2930860.5483 1595972.1827000007, 2927031.2744999994 1585948.0746, 2912633.832699999 1582546.5112999994, 2896409.0803999994 1593439.6593999993, 2888152.7097999994 1605791.4318000004, 2877072.045600001 1609936.5909000002, 2853957.317 1668880.8277000003, 2853475.7518000007 1676543.7486000005, 2862160.9350000005 1681571.7458999995, 2817387.2651000004 1732249.2284999993, 2777974.267000001 1743031.7994)</t>
+  </si>
+  <si>
+    <t>934 (with 684)</t>
+  </si>
+  <si>
+    <t>MULTIPOLYGON (((3548589.0701 1799185.7504999992, 3560772.0286 1820484.6421000008, 3588739.0264 1813043.897500001, 3569606.5536 1788720.7510000002, 3548589.0701 1799185.7504999992)), ((3748220.9123 1879825.1542000007, 3756255.0975 1864875.0741000008, 3734530.7139 1834377.9974000007, 3718504.1807000004 1825568.6118, 3697085.4814 1838182.2444000002, 3685691.3013000004 1861505.6067999993, 3675220.1215000004 1850663.7595000006, 3666499.883300001 1865968.3651, 3700964.147399999 1891478.3967000004, 3722706.4079 1898039.2884999998, 3731040.7194999997 1879794.6481999997, 3748220.9123 1879825.1542000007)), ((3798550.3234 1899270.0248000007, 3820936.3209000006 1909529.2749000005, 3838965.128900001 1880982.3159999996, 3821291.6811999995 1875259.8915, 3798550.3234 1899270.0248000007)), ((3718113.155200001 2089575.7193999998, 3618795.3077000007 2049423.9584, 3556316.2591999993 2032334.2839000002, 3538321.442500001 2011972.7665999997, 3515777.0196 1986674.8182999995, 3445577.7430000007 1906510.609099999, 3431717.7398000006 1869960.1678999998, 3447420.7983999997 1813123.3479999993, 3460823.1437 1791282.0977999996, 3406426.3587999996 1762027.7755999994, 3370291.3166000005 1707909.2694000006, 3287208.5506999996 1667564.6730000004, 3270542.1349 1648420.2855999991, 3259019.3167000003 1635251.5614999998, 3236982.2836000007 1610217.8969, 3175488.4696999993 1617310.9110000003, 3144922.6086 1621046.3414999992, 3123117.7705000006 1624308.2484000009, 3087263.7814000007 1629828.3533999994, 3033301.7106 1635460.8302999996, 2948813.8093 1608501.5980999991, 2938041.8399 1592776.9705999997, 2935429.5359000005 1593682.6921999995, 2930860.5483 1595972.1827000007, 2927031.2744999994 1585948.0746, 2912633.832699999 1582546.5112999994, 2896409.0803999994 1593439.6593999993, 2888152.7097999994 1605791.4318000004, 2877072.045600001 1609936.5909000002, 2853957.317 1668880.8277000003, 2853475.7518000007 1676543.7486000005, 2862160.9350000005 1681571.7458999995, 2817387.2651000004 1732249.2284999993, 2777974.267000001 1743031.7994, 2776212.4310999997 1783297.5351, 2785763.5819000006 1800101.8616000004, 2841367.7413999997 1845643.4425000008, 2825810.8137 1846890.8708999995, 2817367.6576000005 1878991.0332999993, 2830219.0867999997 1909755.1043999996, 2851525.2676 1934571.5063000005, 2839691.3215999994 1967475.0245999992, 2822316.5429 2015259.6797000002, 2868562.2829 2012858.7808999997, 2885229.647399999 2068270.8232000005, 2892686.5370000005 2068076.5185000002, 2903686.877800001 2094913.7258000001, 2904457.601 2151677.7938, 2928114.7364000008 2166294.6163, 2947304.8771 2172124.7914000005, 2968508.660700001 2201289.1238, 2947976.512700001 2240662.4060999993, 2921462.8126999997 2255028.6382999998, 2901984.571900001 2249097.1273999996, 2831796.0873000007 2259162.0669, 2822605.4909000006 2261163.0436000004, 2828168.7161 2298249.038899999, 2767741.0801 2281168.122199999, 2785736.7751 2329544.0899, 2799517.0140000004 2366660.8057000004, 2779356.7490999997 2365202.441400001, 2768931.5584999993 2408013.3790000007, 2777570.198999999 2417446.5478000008, 2793854.0087 2435304.5789, 2823820.7687 2434649.0449, 2849078.9859999996 2434213.8176000006, 2906664.9859999996 2459935.7007999998, 2912845.0681 2451346.838199999, 2954461.5582999997 2426794.9991999995, 3048810.573999999 2413341.8238999993, 3150432.1084000003 2367561.8840999994, 3241371.8056000005 2352092.7432000004, 3257969.7192 2342918.488500001, 3288670.385500001 2346255.619999999, 3313142.3012000006 2331293.032299999, 3340071.2053999994 2326830.8924000002, 3358653.794399999 2325035.2841999996, 3367335.8532 2324216.1876, 3368407.7152999993 2322270.5248000007, 3371028.6866999995 2317520.1096, 3393705.6569999997 2309700.1274999995, 3446154.712200001 2264004.4198000003, 3478445.4934 2251519.461100001, 3540709.943499999 2226544.1711, 3555449.739 2223671.0808000006, 3563128.5130000003 2229190.7112000007, 3573288.5988999996 2236521.7369, 3610160.1626999993 2218084.5045999996, 3618228.6633 2206417.9881999996, 3621045.8857000005 2191586.128900001, 3640254.1414 2192873.1951, 3640544.7918999996 2191503.195699999, 3758412.626 2173293.2490999997, 3745684.4419 2120436.249500001, 3718113.155200001 2089575.7193999998)))</t>
+  </si>
+  <si>
+    <t>Row correction value</t>
+  </si>
+  <si>
+    <t>Ready?</t>
+  </si>
+  <si>
+    <t>867 (with 862)</t>
+  </si>
+  <si>
+    <t>LINESTRING (4121719.5385 2300472.5979999993, 4114290.4915999994 2296841.2978000008, 4112225.4616 2294422.3629)</t>
+  </si>
+  <si>
+    <t>MULTIPOLYGON (((4257347.9024 2041659.8243000004, 4236115.923900001 2046352.6637999993, 4228587.3279 2070742.982999999, 4215930.3434999995 2112203.6213000007, 4206959.399700001 2141948.1119999997, 4272737.657500001 2188026.9871999994, 4271177.4068 2084154.0124999993, 4266688.6185 2070299.9861999992, 4257347.9024 2041659.8243000004)), ((3640544.7918999996 2191503.195699999, 3640254.1414 2192873.1951, 3645972.8148 2199964.7068000007, 3618228.6633 2206417.9881999996, 3610160.1626999993 2218084.5045999996, 3573288.5988999996 2236521.7369, 3563128.5130000003 2229190.7112000007, 3555449.739 2223671.0808000006, 3540709.943499999 2226544.1711, 3478445.4934 2251519.461100001, 3446154.712200001 2264004.4198000003, 3393705.6569999997 2309700.1274999995, 3371028.6866999995 2317520.1096, 3368407.7152999993 2322270.5248000007, 3367335.8532 2324216.1876, 3391140.7709 2340602.364499999, 3427515.4086000007 2440388.0063000005, 3451405.1644 2543018.3781000003, 3482989.9301999994 2528820.6995, 3457113.9517 2585136.346000001, 3464111.6295 2643534.1921999995, 3420152.1384999994 2673330.4977, 3414050.9527000003 2687679.066299999, 3407138.6264999993 2704063.3279999997, 3414068.5150000006 2730767.9806999993, 3385828.4147999994 2782799.1964999996, 3363646.7588 2799697.4349000007, 3338781.8299000002 2790544.7408000007, 3323013.6382 2823439.8303999994, 3314789.6072000004 2840825.3693000004, 3256614.5375999995 2855614.9738, 3259545.8423999995 2886464.0923999995, 3243119.5627999995 2916492.9441, 3264231.5483 2938073.443, 3320985.1766999997 2931509.0515, 3343000.508300001 2935486.1711, 3362406.0352999996 2939072.3869000003, 3382724.117799999 2911833.1833999995, 3442783.7885999996 2896432.291099999, 3471713.9855000004 2901644.076199999, 3473345.5108000003 3001726.1877999995, 3500005.7974999994 3008007.1742000002, 3515982.0009000003 2973170.9476999994, 3619366.6592999995 2970507.3045000006, 3644488.9839999992 2968707.3280999996, 3648739.0617999993 2975371.7832999993, 3652782.7069000006 2976094.3311, 3652817.7008999996 2976375.3478999995, 3652852.695800001 2976656.3649000004, 3608006.2128999997 2984295.780200001, 3621889.076300001 3003960.126599999, 3657641.5549999997 3015040.5424000006, 3705361.3970999997 3030981.6422000006, 3727768.7654999997 3060350.0757, 3726112.350400001 3087332.4086000007, 3734384.2558999993 3117049.5149000008, 3765498.250600001 3129649.2190000005, 3799789.3935000002 3135288.8575, 3802065.476500001 3115282.907400001, 3817784.9420999996 3090853.9849999994, 3818208.9650999997 3090203.6359, 3819380.580499999 3090402.751, 3820232.0768999998 3088929.274599999, 3820865.0940000005 3089001.2928, 3821127.0906000007 3089941.3904, 3821872.7488 3089834.652899999, 3822511.539000001 3090764.4552999996, 3822702.193499999 3092377.1894000005, 3823205.976399999 3092752.3683, 3823719.6410000008 3092926.2487000003, 3823373.370100001 3093872.069700001, 3823576.295499999 3094429.0299999993, 3824816.5967999995 3095157.707699999, 3825314.076199999 3094776.3259999994, 3825882.0142 3094749.912900001, 3826732.1295 3095446.3819999993, 3828413.9506 3096281.0318, 3828830.3148999996 3096701.8082, 3829124.514799999 3097051.1959000006, 3829391.7752 3097020.708799999, 3835046.9453999996 3097095.6535, 3844678.012599999 3088813.8804, 3853161.5405 3069289.1185, 3868536.232000001 3061788.467599999, 3871119.5032 3058361.0966, 3876165.7367000002 3046342.8936, 3896518.9996000007 3044671.3225, 3901203.5385999996 3001917.1602, 3907618.9147999994 2999071.3099000007, 3921742.4297 2996168.7018, 3949129.2158000004 3017066.643100001, 3959123.5232999995 2977871.6417999994, 3971752.4340000004 2967666.1932999995, 3988312.6208999995 2955361.1799, 3993083.8806999996 2941704.5809000004, 4012456.508300001 2945942.9268999994, 4018497.2259 2945664.4036, 4023633.5628999993 2939874.9432999995, 4057753.9418 2935021.0808000006, 4071243.3954000007 2928770.9639, 4082335.1054 2905956.7978000008, 4109552.371200001 2897821.1248000003, 4121360.4156 2894898.5023, 4129088.6479 2897694.362400001, 4148169.9397 2885085.8198000006, 4168238.4449000005 2883501.2454000004, 4179638.1773000006 2878090.5392000005, 4191568.4299 2874149.0747999996, 4170832.9875000007 2847105.0318, 4148737.4970999993 2796455.1335000005, 4140622.8365 2781605.5660999995, 4140555.6732 2780969.7829, 4140149.0461 2758618.4416000005, 4136889.5688000005 2739716.5875000004, 4139577.4244 2722539.9049999993, 4136938.8966000006 2719812.1586000007, 4133383.940300001 2713039.7738000005, 4123319.4144 2705527.9356999993, 4104716.988399999 2714128.7832999993, 4090009.1479 2707007.728700001, 4082697.7651000004 2677681.3720999993, 4082827.792300001 2677478.4815999996, 4051112.1227 2643952.642999999, 4024713.6202000007 2612631.9044000003, 4018233.3856000006 2597241.8249999993, 4022416.092599999 2586011.9647000004, 4008290.6635999996 2566176.7631, 4025672.9941000007 2570762.0755000003, 4031470.0842000004 2588477.0012999997, 4048975.1100999992 2597449.4472000003, 4076472.880999999 2595665.6992000006, 4091539.9584999997 2538951.4132000003, 4072064.4948999994 2523773.4279999994, 4094309.3320000004 2488413.1999999993, 4095551.4164000005 2465999.3100000005, 4055455.9967 2450215.5264, 4088123.4881999996 2404818.9069, 4078566.3036 2398682.6088999994, 4072437.7837000005 2366359.4788000006, 4137476.9604 2330752.1697000004, 4121719.5385 2300472.5979999993, 4114290.4915999994 2296841.2978000008, 4112225.4616 2294422.3629, 4072166.411800001 2268612.8674999997, 4032631.8049999997 2234461.5803999994, 3968344.3807999995 2240334.946900001, 3853357.737400001 2279282.4799000006, 3843684.6764 2290546.8387, 3798359.9470000006 2270509.5507999994, 3785157.6610000003 2264759.6624999996, 3771048.433 2258657.5887, 3751465.3564 2218747.8960999995, 3750769.3911000006 2202240.7512, 3758412.626 2173293.2490999997, 3640544.7918999996 2191503.195699999)))</t>
+  </si>
+  <si>
+    <t>1052, 1053, 1055, 1058, 1075, 1076</t>
+  </si>
+  <si>
+    <t>MULTIPOLYGON (((3919814.3946 3153328.4564999994, 3900841.3057000004 3141114.0470000003, 3892268.487299999 3140257.5569, 3859809.09 3150168.8783, 3859737.4079 3160854.8641999997, 3919814.3946 3153328.4564999994)), ((3883442.9903999995 3175162.1089999992, 3896190.6349 3201061.1819, 3918217.2456 3226298.0676000006, 3923497.8717 3231860.2903000005, 3936686.5755000003 3245668.6426, 3946030.5296 3260714.0299999993, 3951477.2358999997 3272490.5833, 3955930.2215 3287337.5961000007, 3960097.4846 3307432.2420000006, 3971473.9976000004 3356963.5716999993, 3996616.1115000006 3332178.267999999, 4014218.2829 3347857.646400001, 4022186.940199999 3358879.6272, 4046788.7599 3371594.909, 4067837.936899999 3373652.2719, 4085028.9791 3374111.0285, 4113226.3334999997 3371154.9495, 4127371.2161999997 3353524.3608, 4134707.5439999998 3351905.1378000006, 4133736.155200001 3337487.729699999, 4125134.6445000004 3307187.4432999995, 4118393.6692999993 3285247.0691, 4098287.6952 3284897.710999999, 4096766.4867000002 3269198.322899999, 4117146.8552 3258660.1053, 4120624.0736 3240894.579399999, 4099187.351500001 3228125.133300001, 4092852.0757999998 3207673.7051, 4073465.7522 3196970.059800001, 4057369.1633 3205892.865700001, 4041680.6645 3189693.8340000007, 4058181.026799999 3146140.6393999998, 4046900.025699999 3133097.6772000007, 4053685.3247999996 3126266.0513000004, 4031952.4076000005 3110464.237400001, 4045944.8244000003 3096437.1327, 4040360.1849000007 3079039.3890000004, 4025883.6818000004 3075418.9510999992, 4017252.1834999993 3086772.5351, 4024033.4265 3108310.8542, 4026610.5578000005 3113861.8872999996, 4011459.8396000005 3132703.4902999997, 3988851.4396 3138673.9134, 3980658.9135 3157888.2239999995, 3957506.818499999 3167694.4761999995, 3950633.7397000007 3159702.9375, 3923161.9311999995 3156164.4332, 3920660.2127 3156217.704, 3883442.9903999995 3175162.1089999992)))</t>
+  </si>
+  <si>
+    <t>1008, 1322</t>
+  </si>
+  <si>
+    <t>POLYGON ((4291125.0428 2660883.3062999994, 4332066.8737 2637515.7503999993, 4356848.7469999995 2638051.4913, 4355774.3639 2602036.5163000003, 4334343.9449000005 2607397.545600001, 4324907.0221 2580200.1414, 4270832.195599999 2595632.4387, 4262968.432399999 2569255.1774000004, 4256006.521 2562205.0749999993, 4236365.010399999 2524805.7344000004, 4221436.720000001 2554668.332800001, 4196776.6841 2594561.0877, 4156152.8649000004 2537251.1045999993, 4155107.7885999996 2536147.715, 4091539.9584999997 2538951.4132000003, 4076472.880999999 2595665.6992000006, 4048975.1100999992 2597449.4472000003, 4031470.0842000004 2588477.0012999997, 4025672.9941000007 2570762.0755000003, 4008290.6635999996 2566176.7631, 4022416.092599999 2586011.9647000004, 4018233.3856000006 2597241.8249999993, 4024713.6202000007 2612631.9044000003, 4051112.1227 2643952.642999999, 4082827.792300001 2677478.4815999996, 4082697.7651000004 2677681.3720999993, 4090009.1479 2707007.728700001, 4104716.988399999 2714128.7832999993, 4123319.4144 2705527.9356999993, 4133383.940300001 2713039.7738000005, 4136938.8966000006 2719812.1586000007, 4139577.4244 2722539.9049999993, 4142867.4965000004 2719235.8000000007, 4148792.7694000006 2716636.1911999993, 4162515.182499999 2721450.2731999997, 4202525.681600001 2718363.0526, 4209312.1808 2724853.3637000006, 4209278.492900001 2741411.866699999, 4217105.1602 2744025.8792000003, 4220591.664899999 2731159.9717999995, 4221123.476 2731035.9192999993, 4259528.3868 2727259.0359000005, 4283009.073799999 2715444.941299999, 4287756.7698 2714352.1854, 4285464.4256 2684223.103700001, 4281155.7798 2659947.7641000003, 4291125.0428 2660883.3062999994))</t>
+  </si>
+  <si>
+    <t>POLYGON ((5787847.8748 3444371.5252, 5733570.6416 3417705.5022, 5722651.774499999 3373609.860200001, 5729662.489600001 3335175.8210000005, 5697532.5516 3344818.5868999995, 5649322.578500001 3323500.0744000003, 5623484.6787 3338741.5080999993, 5609105.198000001 3312077.5097000003, 5568486.086999999 3326331.3630999997, 5539611.837099999 3305695.2524999995, 5489601.131999999 3320921.044399999, 5367193.8565 3314815.0901999995, 5309900.3697 3294184.1675000004, 5260075.682 3243410.1711, 5251592.694599999 3262450.6114000008, 5250671.5485 3303593.9591000006, 5214670.998199999 3322722.8641999997, 5251371.4409 3377815.090399999, 5250768.1742 3400147.626, 5236429.878900001 3437174.9952000007, 5212596.743899999 3482699.7271, 5202339.4189 3510354.4520999994, 5264627.805199999 3519688.9715, 5282724.105799999 3548285.2378000002, 5334687.998299999 3564716.6867999993, 5331054.435699999 3607861.5889999997, 5326369.9383000005 3631446.2008999996, 5334161.9756000005 3651099.0450999998, 5347477.6841 3660179.2818, 5351501.5657 3675907.1116000004, 5371400.884400001 3683815.693499999, 5374609.0176 3696416.7972999997, 5356923.878900001 3740090.5593, 5412479.6875 3775879.8604000006, 5435586.0679 3815982.9613000005, 5607235.8376 3801217.2039, 5652484.480799999 3702928.9570000004, 5736255.046599999 3632589.2755999994, 5763788.8858 3631150.6728000008, 5792311.692500001 3607912.7852999996, 5794683.890699999 3587422.5714999996, 5732331.7488 3535698.741800001, 5787847.8748 3444371.5252))</t>
+  </si>
+  <si>
+    <t>POLYGON ((3173848.043400001 3612488.6251, 3195615.0461999997 3589512.522399999, 3214939.132200001 3602580.7288000006, 3235160.6678 3596830.425899999, 3245165.7368 3577208.328400001, 3244775.7710999995 3561762.7819999997, 3267014.1543000005 3563205.9560000002, 3258608.927100001 3511383.283, 3263290.492900001 3493217.353700001, 3255316.576199999 3463709.3354, 3240880.3333 3412798.4442, 3205614.5670999996 3361773.0997, 3108541.1415999997 3354476.7108999994, 2978351.1560999993 3337521.957699999, 2945859.5538999997 3376722.8989000004, 2965101.1202000007 3427072.1415999997, 3025762.0605999995 3449549.3127999995, 3035185.5490000006 3491156.8958, 3065671.0968999993 3502790.1567, 3016105.5384 3538827.9297, 3005532.8137 3570044.7643999998, 3019430.190199999 3589715.1007000003, 3018438.1960000005 3617603.3116999995, 3042558.8431 3639689.5074000005, 3087910.4957999997 3615179.6028000005, 3142931.390900001 3637196.670600001, 3133726.9563999996 3663079.7677999996, 3170810.707800001 3705282.9833000004, 3233385.166099999 3710083.0327000003, 3230329.8203999996 3682748.466600001, 3197575.4376 3657011.4365999997, 3199284.5310999993 3641564.6778999995, 3173848.043400001 3612488.6251))</t>
+  </si>
+  <si>
+    <t>1091, 1109</t>
+  </si>
+  <si>
+    <t>MULTIPOLYGON (((3383213.079500001 3440412.3221000005, 3366761.349199999 3427444.3366, 3354541.1807000004 3456996.0320999995, 3379028.088300001 3463201.7961999997, 3383213.079500001 3440412.3221000005)), ((3472384.513800001 3481603.9678000007, 3461943.4733000007 3481447.4974000007, 3464057.1643000003 3491282.1532000005, 3471740.8751999997 3502049.3111000005, 3472384.513800001 3481603.9678000007)), ((3326115.635 3613225.0734, 3325818.2509000003 3586023.142999999, 3320894.7715000007 3580735.0478000008, 3316939.8149999995 3592764.4944, 3313863.0731000006 3576299.1032, 3285069.8533999994 3554456.8554999996, 3267014.1543000005 3563205.9560000002, 3244775.7710999995 3561762.7819999997, 3245165.7368 3577208.328400001, 3235160.6678 3596830.425899999, 3214939.132200001 3602580.7288000006, 3195615.0461999997 3589512.522399999, 3173848.043400001 3612488.6251, 3199284.5310999993 3641564.6778999995, 3197575.4376 3657011.4365999997, 3230329.8203999996 3682748.466600001, 3236307.3610999994 3678562.4067, 3252818.8046000004 3689149.8693000004, 3300387.783500001 3689755.908399999, 3309324.5363999996 3662898.0988999996, 3306910.9417000003 3621319.4058999997, 3303772.059800001 3618198.355799999, 3309523.3145000003 3616906.9865000006, 3326115.635 3613225.0734)), ((3331199.3146 3760454.8090000004, 3327236.8691000007 3743384.34, 3321162.7084 3732133.4186000004, 3312182.2248 3728380.5878999997, 3298814.125 3750249.4229000006, 3307297.0935999993 3758116.390900001, 3331199.3146 3760454.8090000004)), ((3328549.5143999998 3879442.5469000004, 3349303.582800001 3900734.3519, 3344391.6415 3914010.6296999995, 3323650.5821 3918920.6352999993, 3323562.6757999994 3931364.1602, 3346925.8308000006 3940906.9964000005, 3358588.4487999994 3958999.2556, 3368083.8198000006 3908537.1206, 3358109.862299999 3877275.5415000003, 3349876.9705 3886091.024599999, 3334528.2785 3863827.9418, 3328549.5143999998 3879442.5469000004)), ((3290299.2507000007 3967784.5231999997, 3315586.690199999 3977884.6323000006, 3316721.9101 4000967.0834, 3334274.2485000007 4023625.898499999, 3377291.8451000005 4038243.118899999, 3378769.583799999 4018108.0732000005, 3361723.1677 3990129.5666000005, 3327092.8494000006 3973344.2128, 3301991.0339 3955779.7521, 3301840.3050999995 3944764.4836999997, 3280061.763800001 3903739.851, 3274896.6346000005 3908116.3292999994, 3287729.4079 3937607.497300001, 3290299.2507000007 3967784.5231999997)), ((3243681.9681 3996998.6468, 3233528.0854 3979584.6098999996, 3217022.0209 3996130.930400001, 3218031.1114000008 4015194.707800001, 3243681.9681 3996998.6468)), ((3315661.445699999 4048203.3432, 3303501.890900001 4021070.512599999, 3285166.8161999993 4028794.6963, 3283557.2699999996 4039540.0404000003, 3315661.445699999 4048203.3432)), ((3522551.3373000007 3139323.5561999995, 3539420.0056999996 3132835.039000001, 3535765.1164999995 3108410.8841999993, 3518486.8004 3111151.4234999996, 3513561.3089000005 3128341.3149999995, 3522551.3373000007 3139323.5561999995)), ((3673905.1149000004 3204464.0983000007, 3681173.7656999994 3201641.8335999995, 3684013.7095 3200542.8089000005, 3683737.4542999994 3197132.6165999994, 3680718.2339999992 3198060.7863, 3672442.753799999 3200615.7368, 3673905.1149000004 3204464.0983000007)), ((3645111.9164000005 3196160.2765999995, 3645384.0725 3195936.155099999, 3646115.5846999995 3195333.8921000008, 3647489.7607000005 3194132.056399999, 3647902.5701 3194119.405099999, 3648588.4013 3194235.8268, 3649860.2295999993 3195229.9933, 3650263.100299999 3195054.1955999993, 3650994.660599999 3193365.1898, 3651676.3904999997 3192902.2412, 3652768.864499999 3192561.5485999994, 3653708.6169000007 3192372.6994000003, 3656217.4132000003 3191822.4507, 3657772.6656 3192007.305400001, 3658133.8115999997 3192032.4800000004, 3658424.8598999996 3191987.598099999, 3658830.1218999997 3192230.7797, 3659985.6806000005 3192633.5703999996, 3669373.7040999997 3192660.7994999997, 3670416.2422 3182315.698000001, 3678432.579500001 3180074.4165000003, 3692323.9300999995 3176224.8495000005, 3714279.009299999 3173098.7717000004, 3718156.7750000004 3159923.9596999995, 3687544.3005 3129787.660700001, 3679891.0244999994 3130408.2580999993, 3672050.7456 3129691.793299999, 3615846.2278000005 3124914.9778000005, 3603878.9793999996 3129741.9738999996, 3553352.2958000004 3136848.3926, 3546122.244999999 3135664.585000001, 3534366.0965 3137638.798800001, 3524825.1017000005 3147432.1055999994, 3522689.3104 3148843.6772000007, 3499622.7479999997 3135259.5458000004, 3495970.6580999997 3134147.6164999995, 3492808.174900001 3134525.7272999994, 3485286.7863 3135433.0131, 3480319.294399999 3136038.4222999997, 3423258.2137 3146071.6227, 3412061.7118999995 3148118.8852999993, 3380452.6229999997 3142176.4832000006, 3369080.1911999993 3133124.837200001, 3368336.4393000007 3123718.3510999996, 3362853.4997000005 3119436.7459999993, 3344542.5841000006 3108428.1449999996, 3326732.154100001 3122780.3549000006, 3320727.783399999 3126475.2514999993, 3322251.8126999997 3132619.4716, 3318908.0637999997 3138087.0746, 3246076.8512999993 3105947.9013, 3225411.546 3119549.9806999993, 3306083.6352999993 3192206.2293, 3369157.1538999993 3214448.3686999995, 3392402.0527 3207259.7633999996, 3401610.4755000006 3204446.5611000005, 3420726.5153 3214768.8002000004, 3443456.182600001 3231525.7848000005, 3446880.534499999 3235492.6993000004, 3458893.1213000007 3248428.0107000005, 3449231.922700001 3245831.7205999997, 3440287.8418000005 3242921.3466999996, 3418182.1822999995 3235811.0523000006, 3396103.558 3227337.876, 3379715.6192000005 3239322.0113999993, 3365915.7026000004 3258726.4584999997, 3356470.978599999 3270329.0656000003, 3292872.1479 3275532.2158000004, 3281088.3982999995 3296440.5736, 3382753.9767000005 3361870.9650999997, 3363477.7205999997 3414599.955, 3392606.814099999 3438782.4625000004, 3435926.8509 3440955.7751, 3453179.0140000004 3428337.3719999995, 3452256.0638999995 3433065.543400001, 3455781.6843 3444576.0884000007, 3464414.4016999993 3432207.4518, 3473828.511499999 3431100.3741999995, 3471545.5427 3433575.1773000006, 3471269.745100001 3434116.4317000005, 3461783.0678000003 3447439.755000001, 3460571.7983999997 3462266.2422, 3470406.6829000004 3475254.0593999997, 3481999.7444 3476443.699100001, 3474370.2081000004 3491917.5001999997, 3481171.6976999994 3504640.4196000006, 3485612.7661000006 3526832.8169, 3466270.4267999995 3521147.6422000006, 3449638.3654999994 3576478.7024000008, 3466493.3277000003 3603700.755999999, 3485013.3154000007 3612131.7843999993, 3490108.832699999 3617887.9864000008, 3469108.7453000005 3615722.4952000007, 3390817.9201999996 3608523.877699999, 3360498.1899999995 3628303.6657, 3366151.2761000004 3643820.5701, 3386061.114600001 3676921.7895, 3403235.1805000007 3701218.310799999, 3393176.3049999997 3718031.5385, 3396189.7875999995 3737426.8367999997, 3404090.6919 3744589.569, 3418028.6960000005 3738400.954399999, 3418311.8077000007 3739744.0424000006, 3411164.9464999996 3748588.319599999, 3412436.513699999 3771494.1021999996, 3367217.3351000007 3706570.103599999, 3331175.6340999994 3694016.7129999995, 3358646.0046999995 3790644.9536000006, 3335896.3959 3826324.2882000003, 3356677.025800001 3841124.7876999993, 3379703.289000001 3895854.5447000004, 3395470.4689000007 3908044.5418999996, 3402307.123400001 3954367.1148000006, 3444221.9256999996 4007273.5207, 3516378.957800001 4000440.584899999, 3461377.2294999994 3908521.089299999, 3526308.051000001 3910506.171599999, 3561339.2410000004 3911995.5756, 3608638.9376999997 3876201.1593999993, 3564651.011600001 3804905.2749000005, 3557178.754899999 3793273.4517, 3544610.5228000004 3781610.8419000003, 3520820.005000001 3779174.6586000007, 3504922.8270999994 3769882.3027, 3523749.864499999 3761757.653000001, 3524674.9047 3761007.8731999993, 3525336.9879 3759730.4869, 3525668.9832000006 3758050.5857999995, 3525635.2189000007 3756147.8487, 3525238.9310999997 3754225.8895999994, 3524522.0749999993 3752490.4735000003, 3523561.0242 3751127.4614000004, 3522452.3114 3750270.921599999, 3492175.3694 3735817.744000001, 3491442.9005999994 3735536.3309000004, 3490943.6347000003 3735794.368899999, 3490540.6437999997 3735610.047700001, 3491163.5877 3735221.917199999, 3490958.5294000003 3734671.7301000003, 3490982.1525999997 3734085.6359, 3490704.707800001 3733512.7686, 3490464.1711 3733891.4243, 3490002.7576 3734037.5157999992, 3489798.4845000003 3734555.7074999996, 3489509.2781000007 3734928.7214, 3487951.1191000007 3735870.2672000006, 3487607.7661000006 3735750.5703, 3487455.8946 3735586.2271999996, 3487140.885399999 3735898.130000001, 3487021.2194999997 3736571.0928000007, 3485477.058700001 3737664.5031000003, 3484369.6795000006 3737854.2731, 3483637.0876 3738803.7672000006, 3482920.1790999994 3738766.213199999, 3481977.9728999995 3739044.963199999, 3481487.5231999997 3739543.908399999, 3481291.1514999997 3740279.187000001, 3480479.4678000007 3741395.2544, 3479690.1845999993 3741590.4471000005, 3479796.3083999995 3741079.0304000005, 3479648.2091000006 3740586.280099999, 3479429.854800001 3740301.4148999993, 3479084.8194999993 3740206.1432000007, 3478326.5624 3740414.3312, 3478087.4659 3741341.6372999996, 3477872.3945000004 3741541.8861, 3475853.1797 3741607.4999, 3474502.908500001 3741154.1174, 3473612.2061 3741495.1423000004, 3472456.643100001 3742587.1599000003, 3471612.6098999996 3744338.2337999996, 3470941.1975 3745423.005000001, 3470390.576300001 3745756.9535000008, 3469946.0787000004 3746131.9934, 3469714.4483000003 3746327.465500001, 3469073.2711999994 3747565.7523999996, 3468322.8246 3749052.8411, 3467717.150699999 3749732.7134000007, 3466777.0512000006 3749967.7907999996, 3466009.9483000003 3749202.325099999, 3465947.8029999994 3749429.5637999997, 3465885.6690999996 3749656.803099999, 3466307.9283000007 3749946.4814999998, 3466363.441400001 3750432.5171000008, 3466002.6005000006 3750936.7545, 3465246.8282999992 3751552.8563, 3464716.3987000007 3751446.8038999997, 3464589.2579999994 3751204.030200001, 3464379.5854 3750347.5122999996, 3464000.8476 3750091.9043000005, 3464308.6897 3750073.539999999, 3464481.2061 3750174, 3464710.008199999 3750504.0901999995, 3464747.5134999994 3751192.056399999, 3465158.1717000008 3750993.2531000003, 3465740.550899999 3750629.5096000005, 3465405.4881999996 3749797.9092999995, 3465486.8072999995 3749154.8594000004, 3465772.1340999994 3748836.931, 3466493.0143 3748684.1750000007, 3472509.4506 3738956.1317, 3482977.0286999997 3734488.7936000004, 3488330.0065 3732534.954500001, 3508634.7518000007 3723383.9762999993, 3552262.0264 3715465.689200001, 3570116.0853000004 3697125.9514000006, 3576951.0308 3684729.3123000003, 3582187.912799999 3675297.9571, 3589903.4712000005 3661272.846999999, 3590374.2598 3636825.9058999997, 3592155.2672000006 3610215.7831999995, 3595987.894200001 3594899.253900001, 3595544.8106999993 3585543.0714999996, 3599768.0418 3569285.7589, 3599388.4892999995 3553305.4936999995, 3625708.122300001 3546887.1467000004, 3656090.2706000004 3496747.442399999, 3654434.0238000005 3476708.7763, 3660686.4996000007 3452358.1659999993, 3644569.4272000007 3454641.7156000007, 3635823.5885000005 3450747.5012, 3617033.8850999996 3449572.4760999996, 3636536.3488999996 3447545.7858000007, 3661305.2819999997 3425260.6345000006, 3673865.431399999 3390409.7146000005, 3658415.1522000004 3356366.1446, 3666864.9111 3344046.1195, 3700407.666099999 3351757.2805000003, 3714435.7141999993 3355058.8991, 3739365.8357999995 3346662.9119000006, 3760200.0012 3324800.736300001, 3761888.236300001 3300995.782299999, 3741353.467599999 3254283.0979999993, 3707889.301999999 3242284.7193, 3697392.159600001 3219210.3500999995, 3682807.2401 3214473.0602, 3671573.747300001 3210859.3913000003, 3671064.6777999997 3198229.4825, 3664855.6209999993 3200561.199100001, 3654719.1642000005 3193810.1154999994, 3643416.5744000003 3198789.3972999994, 3636000.4470000006 3202680.2786, 3629855.9514000006 3202560.5429999996, 3623764.2393999994 3203484.5467000008, 3621681.0913999993 3203977.2249, 3627185.7415999994 3200517.068499999, 3643744.4990999997 3197624.8969, 3644571.4089 3196739.092700001, 3645111.9164000005 3196160.2765999995)), ((3586365.9486999996 4090902.0452999994, 3592915.4421999995 4072843.4612000007, 3563497.8523999993 4038565.3890000004, 3554208.6147000007 4051883.8549000006, 3560861.3423999995 4068427.6435000002, 3586365.9486999996 4090902.0452999994)), ((3593740.2541000005 4055352.8071, 3592915.4421999995 4072843.4612000007, 3592901.6460999995 4074583.4755000006, 3606123.0395 4088442.5928000007, 3606912.4069 4064160.0808000006, 3593740.2541000005 4055352.8071)), ((3684494.3236 4153634.158399999, 3702441.7358 4135469.3718999997, 3687478.035700001 4118856.2644999996, 3680383.8899000008 4129673.9451, 3676998.8725000005 4139731.5579000004, 3684494.3236 4153634.158399999)), ((3700198.2906 4210128.8355, 3708946.5778 4200874.598099999, 3713935.3204999994 4230457.3116, 3728995.7130999994 4228088.228, 3703741.4136999995 4175490.5814999994, 3692924.8807999995 4162960.7914000005, 3692417.0890999995 4197913.5425, 3700198.2906 4210128.8355)))</t>
+  </si>
+  <si>
+    <t>1042, 1010, 1023, 1011, 1048, 1049</t>
+  </si>
+  <si>
+    <t>MULTIPOLYGON (((4136889.5688000005 2739716.5875000004, 4140149.0461 2758618.4416000005, 4140555.6732 2780969.7829, 4140622.8365 2781605.5660999995, 4148737.4970999993 2796455.1335000005, 4170832.9875000007 2847105.0318, 4191568.4299 2874149.0747999996, 4179638.1773000006 2878090.5392000005, 4168238.4449000005 2883501.2454000004, 4148169.9397 2885085.8198000006, 4129088.6479 2897694.362400001, 4121360.4156 2894898.5023, 4109552.371200001 2897821.1248000003, 4082335.1054 2905956.7978000008, 4071243.3954000007 2928770.9639, 4057753.9418 2935021.0808000006, 4059130.7711999994 2944039.3893999998, 4067410.837099999 2973721.5833, 4044953.8672 3009232.5731000006, 4065087.3355 3029745.6953, 4059686.3597 3049366.0593999997, 4040360.1849000007 3079039.3890000004, 4045944.8244000003 3096437.1327, 4031952.4076000005 3110464.237400001, 4053685.3247999996 3126266.0513000004, 4046900.025699999 3133097.6772000007, 4058181.026799999 3146140.6393999998, 4041680.6645 3189693.8340000007, 4057369.1633 3205892.865700001, 4073465.7522 3196970.059800001, 4092852.0757999998 3207673.7051, 4099187.351500001 3228125.133300001, 4120624.0736 3240894.579399999, 4117146.8552 3258660.1053, 4096766.4867000002 3269198.322899999, 4098287.6952 3284897.710999999, 4118393.6692999993 3285247.0691, 4125134.6445000004 3307187.4432999995, 4133736.155200001 3337487.729699999, 4134707.5439999998 3351905.1378000006, 4138750.3600999992 3360935.3455999997, 4127540.2368 3366604.9955, 4155275.4101 3399818.1371999998, 4176382.6543000005 3402209.9497999996, 4194751.966399999 3393946.6743, 4197878.8917 3384615.9682, 4192372.5107000005 3379297.522500001, 4201005.0361 3368299.9952000007, 4225157.210200001 3380666.8516000006, 4223056.660599999 3389733.5266999993, 4229550.3774 3407325.4558000006, 4234678.0746 3421310.459899999, 4244479.204 3435836.931, 4245717.2721 3462796.1393, 4233488.610400001 3534838.2576, 4249689.6296999995 3532312.2336999997, 4264045.7861 3530123.4396, 4274283.7929 3523118.9946999997, 4283856.6886 3525296.4646000005, 4286822.7674 3523626.4880999997, 4288333.1447 3524216.9692, 4306700.0561999995 3513563.8450000007, 4307694.2598 3495169.0646, 4331938.636299999 3480738.1951, 4332328.8266 3471046.3947, 4367472.4155 3466735.8474000003, 4386496.9418 3468978.9275, 4376190.2784 3431980.1624999996, 4380328.672700001 3428122.1577000003, 4423356.629799999 3436786.9388999995, 4451511.6183 3453830.8413999993, 4464496.873 3461970.9582, 4469893.0550999995 3465507.3104999997, 4531387.9187 3500546.8101000004, 4551177.835899999 3486755.055299999, 4537621.657299999 3459061.6147000007, 4598483.263599999 3432717.9909000006, 4598024.352 3425758.6513, 4591126.8651 3414092.931500001, 4602721.2754999995 3407226.048800001, 4614776.206 3366892.3253000006, 4599281.9924 3324914.319700001, 4600578.1602 3317654.933700001, 4620842.0239 3294804.2860000003, 4629911.4213 3289187.701199999, 4629435.833000001 3263563.6764, 4634821.9384 3250189.340500001, 4646802.7424 3228426.8564999998, 4644664.8412999995 3220609.5798000004, 4648590.561000001 3174085.7885, 4667129.407400001 3151023.3308000006, 4660255.7794 3095529.1428999994, 4645979.160499999 3093185.0231999997, 4635755.0407 3113254.6547, 4623550.103499999 3113763.4321, 4613160.545 3090520.4581000004, 4578743.5452 3075177.8411, 4568654.602399999 3063911.0807000007, 4530540.3905 3036694.340399999, 4504645.4372000005 3036024.5754000004, 4470617.443499999 3025026.0146999992, 4475191.6471 3014233.6904000007, 4482881.8697 2996472.522500001, 4504235.755100001 2980138.6501, 4494030.7502999995 2963467.4614000004, 4508712.424799999 2939910.5363999996, 4511863.501 2932678.570699999, 4552189.4165 2900592.4167, 4571071.8972 2879894.6663000006, 4581003.231000001 2879001.467, 4603174.0754 2858273.119000001, 4600312.774800001 2851666.636, 4596341.521500001 2829133.7541000005, 4579900.4079 2836889.7173999995, 4579671.3643 2836835.5207, 4579445.3671 2836171.4388999995, 4579714.7586 2835384.8275000006, 4579577.8562 2834988.9930000007, 4578831.8160999995 2834529.6916000005, 4578694.752699999 2834033.946799999, 4578256.6741 2833743.7687999997, 4577590.199999999 2833819.306399999, 4577520.554300001 2832996.6304, 4576657.3144000005 2832784.0842000004, 4576129.709899999 2833244.352, 4556759.177300001 2802949.1988999993, 4539906.565199999 2792493.4747, 4525936.166999999 2781511.587099999, 4534508.8895 2768916.1735999994, 4535816.2831 2765181.807, 4542424.854499999 2755742.9772999994, 4550492.988700001 2716598.8374000005, 4523482.837200001 2733534.5822, 4514603.5298 2727668.8101000004, 4496572.345000001 2734271.410700001, 4475984.664100001 2724949.8110000007, 4460729.270300001 2722685.2793000005, 4443880.2947 2721225.526799999, 4427326.055500001 2710091.6841, 4428275.4441 2704501.090399999, 4397789.8456999995 2698611.856899999, 4395879.224099999 2698559.6253999993, 4387765.814200001 2714092.2085999995, 4355225.3652 2715902.9925999995, 4352656.717800001 2697259.9672999997, 4334506.5766 2684074.9562, 4320964.2509 2707711.6807000004, 4318575.4584 2714736.6659999993, 4287756.7698 2714352.1854, 4283009.073799999 2715444.941299999, 4259528.3868 2727259.0359000005, 4221123.476 2731035.9192999993, 4220591.664899999 2731159.9717999995, 4217105.1602 2744025.8792000003, 4209278.492900001 2741411.866699999, 4209312.1808 2724853.3637000006, 4202525.681600001 2718363.0526, 4162515.182499999 2721450.2731999997, 4148792.7694000006 2716636.1911999993, 4142867.4965000004 2719235.8000000007, 4139577.4244 2722539.9049999993, 4136889.5688000005 2739716.5875000004)), ((4210702.8399 3415764.6764, 4221198.286699999 3439472.8971999995, 4236123.1843 3426692.145199999, 4220740.653899999 3412520.1379000004, 4210702.8399 3415764.6764)), ((4166955.4499999993 3464869.876, 4184291.8157 3472667.3577999994, 4194192.7557999995 3462176.4882999994, 4188683.2228999995 3433561.2444, 4166955.4499999993 3464869.876)))</t>
+  </si>
+  <si>
+    <t>POLYGON ((4960290.233100001 2972378.4113999996, 4929608.184 2955255.7161, 4924768.599400001 2945551.253799999, 4881191.0218 2889219.8411999997, 4863380.6556 2882817.0767, 4832035.225400001 2857836.831599999, 4742889.3682 2876362.7248, 4726983.6402 2881333.1931999996, 4689833.4824 2885245.5896000005, 4666960.763 2841107.5930000003, 4603174.0754 2858273.119000001, 4581003.231000001 2879001.467, 4571071.8972 2879894.6663000006, 4552189.4165 2900592.4167, 4511863.501 2932678.570699999, 4508712.424799999 2939910.5363999996, 4494030.7502999995 2963467.4614000004, 4504235.755100001 2980138.6501, 4482881.8697 2996472.522500001, 4475191.6471 3014233.6904000007, 4470617.443499999 3025026.0146999992, 4504645.4372000005 3036024.5754000004, 4530540.3905 3036694.340399999, 4568654.602399999 3063911.0807000007, 4578743.5452 3075177.8411, 4613160.545 3090520.4581000004, 4623550.103499999 3113763.4321, 4635755.0407 3113254.6547, 4645979.160499999 3093185.0231999997, 4660255.7794 3095529.1428999994, 4684723.023800001 3106894.619999999, 4710986.851 3088955.8484000005, 4752267.583900001 3079151.3924000002, 4768791.1215 3072783.737299999, 4790698.883300001 3024479.4278999995, 4810262.3573 3032463.4832000006, 4810829.4825 3060614.4891999997, 4849853.547 3042644.7591999993, 4895030.487 3026304.2892000005, 4935450.206499999 3013499.7408000007, 4960290.233100001 2972378.4113999996))</t>
+  </si>
+  <si>
+    <t>1105, 1107</t>
+  </si>
+  <si>
+    <t>MULTIPOLYGON (((4348493.1647 3530953.34, 4340720.056500001 3530913.743899999, 4306133.109300001 3584922.9717999995, 4323871.3697999995 3607135.3202, 4364880.111199999 3604560.9712000005, 4377517.6185 3548323.9846, 4372610.7994 3530144.287900001, 4348493.1647 3530953.34)), ((4637471.761700001 3554821.074100001, 4620473.755100001 3568132.855900001, 4624296.5853 3584535.6273999996, 4635779.866599999 3578896.6063, 4650436.6755 3566064.9552999996, 4646834.236400001 3554928.2983999997, 4637471.761700001 3554821.074100001)), ((4483442.702199999 3627096.3663999997, 4494202.343 3619375.9897000007, 4486271.765799999 3610440.0326000005, 4478644.9537 3616397.9992999993, 4470058.706900001 3612362.066400001, 4461580.009400001 3593304.3318000007, 4466903.742799999 3569192.7401, 4447265.077199999 3510327.7759000007, 4409463.0046999995 3523907.976399999, 4415598.7502999995 3550646.374399999, 4398888.3050999995 3579315.2716000006, 4398650.158600001 3616062.6950000003, 4416603.817 3640365.8100000005, 4442809.4101 3636989.2061, 4454857.100199999 3667685.5846999995, 4477924.5309 3664114.4546000008, 4478969.6675 3648032.8610999994, 4483003.9076000005 3636653.2402, 4483442.702199999 3627096.3663999997)), ((4371444.760399999 3709872.974300001, 4373684.3467999995 3691339.0622000005, 4317589.2348 3625126.0066, 4300374.668199999 3623120.2839, 4310654.8440000005 3543739.8956000004, 4296791.0067 3530750.5178999994, 4283856.6886 3525296.4646000005, 4274283.7929 3523118.9946999997, 4264045.7861 3530123.4396, 4249689.6296999995 3532312.2336999997, 4233488.610400001 3534838.2576, 4206730.371099999 3607914.155200001, 4207097.7344 3636782.6064999998, 4209646.3386 3718056.8630999997, 4239257.802300001 3714501.1626999993, 4252907.743799999 3735150.0868999995, 4278366.9034 3732415.6337, 4264070.5239 3758783.4650999997, 4253281.521500001 3758473.8757000007, 4242406.2972 3736611.0679, 4218669.1138 3749597.2256000005, 4237985.487600001 3778485.4078, 4253632.164100001 3780310.408399999, 4337943.0417 3832934.8523999993, 4350873.034399999 3805523.0441999994, 4333207.062999999 3731189.0035999995, 4371444.760399999 3709872.974300001)))</t>
+  </si>
+  <si>
+    <t>1094, 1085, 1073, 1046, 1083</t>
+  </si>
+  <si>
+    <t>POLYGON ((5003133.9341 2988592.054199999, 4981146.918199999 2964053.5408999994, 4960290.233100001 2972378.4113999996, 4935450.206499999 3013499.7408000007, 4895030.487 3026304.2892000005, 4849853.547 3042644.7591999993, 4810829.4825 3060614.4891999997, 4810262.3573 3032463.4832000006, 4790698.883300001 3024479.4278999995, 4768791.1215 3072783.737299999, 4752267.583900001 3079151.3924000002, 4710986.851 3088955.8484000005, 4684723.023800001 3106894.619999999, 4660255.7794 3095529.1428999994, 4667129.407400001 3151023.3308000006, 4648590.561000001 3174085.7885, 4644664.8412999995 3220609.5798000004, 4646802.7424 3228426.8564999998, 4634821.9384 3250189.340500001, 4629435.833000001 3263563.6764, 4629911.4213 3289187.701199999, 4620842.0239 3294804.2860000003, 4600578.1602 3317654.933700001, 4599281.9924 3324914.319700001, 4614776.206 3366892.3253000006, 4602721.2754999995 3407226.048800001, 4672679.301000001 3463343.8610999994, 4753691.1339 3515984.9076000005, 4813353.057 3545894.5317, 4852859.773499999 3552930.579399999, 4871927.0243 3530224.727600001, 4901276.725 3508415.4630999994, 4944136.4856 3525194.486300001, 4944637.576400001 3524517.5705999993, 4925940.6598000005 3510876.572899999, 4922206.6141 3502100.9487999994, 4954962.0809 3524883.5679, 4976730.92 3524959.1202000007, 4988318.1765 3525040.8861999996, 5069607.537900001 3528478.2787999995, 5147704.3763999995 3546424.1741000004, 5183759.5777 3540551.7379, 5202339.4189 3510354.4520999994, 5212596.743899999 3482699.7271, 5236429.878900001 3437174.9952000007, 5250768.1742 3400147.626, 5251371.4409 3377815.090399999, 5214670.998199999 3322722.8641999997, 5250671.5485 3303593.9591000006, 5251592.694599999 3262450.6114000008, 5260075.682 3243410.1711, 5271129.0626 3219181.101500001, 5311677.2048 3151424.7452000007, 5280978.566199999 3104580.3881, 5233492.579700001 3019106.4867000002, 5242087.6472 2978646.089400001, 5234032.6688 2964367.443499999, 5144084.4395 2988537.182600001, 5088278.376800001 2978299.3541, 5056054.9975000005 2957982.587099999, 5038951.0986 2947340.4475, 5003133.9341 2988592.054199999))</t>
+  </si>
+  <si>
+    <t>MULTIPOLYGON (((5066259.089 4016324.7841999996, 5083634.980599999 4020511.189099999, 5085144.2182 4000835.0855, 5053057.351399999 3958959.251700001, 5030958.016899999 3957907.4825999998, 5013912.3079 3983248.717599999, 5041779.7689 4011076.019200001, 5041689.998400001 4058791.4165000003, 5068119.089500001 4043693.0704999994, 5066259.089 4016324.7841999996)), ((5297161.5155 3941153.178099999, 5203368.3127 3975554.1010999996, 5192747.907199999 3965598.4433999993, 5167149.6851 3949298.7948000003, 5166521.9147 3996787.3203, 5135024.3961 3990002.0045, 5103396.3761 4016847.963300001, 5090939.0001 4077902.9847999997, 5100683.6543000005 4090791.899599999, 5209290.378799999 4151086.2525999993, 5218019.812100001 4159433.3910000008, 5262087.088099999 4156077.8782, 5333199.4778 4170603.0385999996, 5340949.349300001 4159054.2250999995, 5314985.396600001 4087160.6611, 5354049.6872000005 4004104.4673999995, 5350178.1391 3949790.8620999996, 5297161.5155 3941153.178099999)))</t>
+  </si>
+  <si>
+    <t>1131, 1132, 1147, 1128</t>
+  </si>
+  <si>
+    <t>POLYGON ((5374000.401000001 3938766.4824, 5435586.0679 3815982.9613000005, 5412479.6875 3775879.8604000006, 5356923.878900001 3740090.5593, 5314580.0447 3760461.810900001, 5298223.159499999 3769132.5767, 5231736.936000001 3790696.4021000005, 5192242.198100001 3769546.0725, 5130157.0145 3766126.4203999992, 5114449.1548999995 3771206.5187, 5097787.3825 3764687.1994000003, 5057503.611199999 3759611.2509000003, 5007410.6272 3715789.812999999, 4995327.017000001 3794588.554300001, 5019721.195699999 3883840.9365999997, 5062315.4394000005 3909757.0678000003, 5108900.0502 3874214.467700001, 5134269.051100001 3848234.7097999994, 5162340.052999999 3849279.3166000005, 5171516.0714 3860201.5352, 5181786.1339 3888519.2655999996, 5167149.6851 3949298.7948000003, 5192747.907199999 3965598.4433999993, 5203368.3127 3975554.1010999996, 5297161.5155 3941153.178099999, 5350178.1391 3949790.8620999996, 5374000.401000001 3938766.4824))</t>
+  </si>
+  <si>
+    <t>MULTIPOLYGON (((4996322.788799999 5301735.9025, 4943807.892000001 5250194.7501, 4948346.343599999 5164461.637800001, 4932226.6894000005 5124378.9022, 4889483.3258 5130749.9980999995, 4853855.835899999 5111817.7235, 4801469.590500001 5146847.401900001, 4786541.835899999 5162420.5875, 4781583.823799999 5166481.751, 4770072.6545 5167675.498199999, 4760596.4999 5158082.832699999, 4744757.5046 5136005.0243, 4882630.9618999995 5043779.6998, 4929425.7168000005 4919018.998299999, 4939457.887 4857278.8039, 4967895.5929000005 4811191.227299999, 4971226.650800001 4797934.918099999, 4915519.2436999995 4784777.3561, 4897826.8837 4749343.784600001, 4882949.412699999 4752630.926899999, 4865014.382099999 4706862.0638, 4852405.141799999 4671786.730900001, 4863191.8124 4648471.6743, 4866056.1239 4612841.6285, 4824121.6776 4539689.8155000005, 4784816.1929 4515904.392100001, 4748512.5888 4460124.615900001, 4748689.9761 4441848.693299999, 4708274.867900001 4382150.151799999, 4712400.866699999 4358106.142100001, 4708560.2783 4324518.272500001, 4717890.8456999995 4307525.6906, 4707581.9307 4249823.112400001, 4724601.1691 4193676.019200001, 4802428.181700001 4155190.641899999, 4828639.4246 4099628.105799999, 4813627.897500001 4024026.3301, 4778123.9757 3992595.4799000006, 4756741.1951 4006531.7815000005, 4749146.8927 3979009.009299999, 4713515.568299999 3965892.4120000005, 4730318.3267 3916416.1548999995, 4715177.6598000005 3895576.2678999994, 4723660.3072999995 3846239.482000001, 4714642.3265 3797035.8910000008, 4734261.931299999 3762690.9342, 4722886.927300001 3713585.4924999997, 4707053.106899999 3735827.7872, 4695105.4978 3706695.4233999997, 4680618.7213 3681309.1801999994, 4604192.8281 3670893.6075, 4583909.419 3601419.1911999993, 4522235.599300001 3592091.9229000006, 4487078.975199999 3662743.1703999992, 4499886.534700001 3708681.501700001, 4436222.649900001 3830455.2589999996, 4409723.8868 3876749.5907000005, 4390494.7667 3950683.3049999997, 4390976.5208 3986335.1828000005, 4404885.393100001 3988539.145199999, 4401998.2873 3995041.9647000004, 4373394.358200001 3994669.7545999996, 4359073.0623 4038766.7128999997, 4349264.099199999 4075770.285700001, 4351022.8641 4053305.3901000004, 4339298.0162 4065644.9223999996, 4346422.859300001 4037055.2649000008, 4346757.424699999 4003238.4570000004, 4332808.4957 3989225.238, 4311750.9410999995 3993710.8703000005, 4279980.8333 3964790.1810999997, 4256066.1259 3930741.614600001, 4213958.0448 3894853.0270000007, 4160463.1750000007 3880519.0293000005, 4111864.4394000005 3915147.7860000003, 4063429.7015000004 3969120.2654, 4062753.6042 3997635.1504999995, 4078629.6838000007 4025681.0638999995, 4076161.3388 4060048.1505999994, 4086573.9570000004 4065581.8560000006, 4073655.440199999 4082009.8311, 4067516.0020000003 4048739.5405, 4066964.2595000006 4034093.9768000003, 4049998.9838999994 4016026.338199999, 4050940.9976000004 4049816.8564999998, 4042374.994999999 4151462.1871000007, 4055300.7489 4201493.591600001, 4028865.9942000005 4211714.6258000005, 4043570.6801999994 4246645.327099999, 4050152.8543999996 4300287.329, 4065300.0386999995 4319486.0408, 4065105.2411 4346554.886, 4083259.7125000004 4327950.339, 4082496.217599999 4349753.718699999, 4097728.3377 4347843.539899999, 4127568.786800001 4396800.4233, 4168269.650699999 4431121.757200001, 4202989.6961 4434136.853, 4214590.0529 4479883.995100001, 4251819.0867 4476423.644200001, 4237472.6719 4493230.5568, 4240359.9783 4507768.357000001, 4265630.768100001 4503597.1555, 4273302.1142 4491522.827400001, 4306292.048699999 4506000.9859, 4317480.179400001 4546301.294500001, 4356381.989499999 4589914.0655000005, 4371705.4673999995 4611538.400699999, 4372241.9955 4650389.365599999, 4422522.2082 4658514.7499, 4414948.2951 4727918.163699999, 4427038.187000001 4783167.2206, 4446799.338099999 4822302.992699999, 4459084.3749 4813829.069, 4463487.486099999 4851215.2359, 4480658.793 4880435.3213, 4504124.156300001 4900429.4528, 4524696.8105999995 4973594.759, 4562851.1568 5012393.589400001, 4554861.9410999995 5031191.655300001, 4510750.3848 5023979.508199999, 4510924.7915 5071567.874399999, 4554801.4717999995 5123441.0911, 4564713.3299 5084522.766100001, 4583196.3675999995 5103804.6117, 4613870.429199999 5083916.1098, 4600030.493899999 5146386.755000001, 4653395.6316 5197696.0228, 4662259.460999999 5238895.491900001, 4695441.8423999995 5242799.123400001, 4704025.0338 5215904.151699999, 4727614.4300999995 5214816.611500001, 4730784.409700001 5245331.046499999, 4750208.8379 5236473.608999999, 4759008.738299999 5264464.8967, 4789654.0733 5277247.586300001, 4802859.8138 5328245.774, 4832691.8038 5327944.989, 4889648.5798 5378319.3178, 4903835.0221 5335205.0209, 4971010.6425 5401019.9034, 5001186.657199999 5378718.751599999, 5027555.567600001 5391153.160700001, 5074653.9242 5377303.7195999995, 5089119.8992 5354898.9845, 5089238.543 5313294.950200001, 5121979.895099999 5303618.9924, 5129540.749399999 5289674.165200001, 5129146.861400001 5280535.3759, 5103863.7072 5284239.232899999, 5102943.5492 5264215.5197, 5091069.457800001 5246229.9487, 5072809.138800001 5205674.012399999, 5064258.8256 5266231.4595, 4996322.788799999 5301735.9025)), ((4254760.191500001 4532857.8332, 4258826.624299999 4545550.343, 4281550.8379 4547227.8664, 4274343.7094 4524241.469799999, 4254760.191500001 4532857.8332)), ((4441307.7049 4977366.782199999, 4450605.910700001 5009443.189200001, 4457512.147500001 4989894.115599999, 4449988.1676 4967044.3533, 4441307.7049 4977366.782199999)), ((4483972.0098 5031488.6206, 4489350.8421 5012888.968800001, 4468197.6897 4995011.9517, 4462355.771299999 5003033.091, 4483972.0098 5031488.6206)), ((4838530.404100001 5391087.1763, 4848303.566199999 5361192.332800001, 4838084.864 5358305.1501, 4830628.112500001 5382139.6943, 4838530.404100001 5391087.1763)))</t>
+  </si>
+  <si>
+    <t>MULTIPOLYGON (((4819113.076400001 3791717.662799999, 4817976.391899999 3810697.2008999996, 4808950.644099999 3823345.8236999996, 4812958.930299999 3837542.9165000003, 4806240.5188 3853278.9408, 4823231.8354 3886955.7137, 4837869.4964000005 3900907.4658000004, 4859010.725199999 3904881.4912, 4856709.8451000005 3882759.2256000005, 4845993.246200001 3871328.3907999992, 4848366.974300001 3829771.1625999995, 4819113.076400001 3791717.662799999)), ((4971226.650800001 4797934.918099999, 4915519.2436999995 4784777.3561, 4897826.8837 4749343.784600001, 4882949.412699999 4752630.926899999, 4865014.382099999 4706862.0638, 4852405.141799999 4671786.730900001, 4863191.8124 4648471.6743, 4866056.1239 4612841.6285, 4824121.6776 4539689.8155000005, 4784816.1929 4515904.392100001, 4748512.5888 4460124.615900001, 4748689.9761 4441848.693299999, 4708274.867900001 4382150.151799999, 4712400.866699999 4358106.142100001, 4708560.2783 4324518.272500001, 4717890.8456999995 4307525.6906, 4707581.9307 4249823.112400001, 4724601.1691 4193676.019200001, 4802428.181700001 4155190.641899999, 4828639.4246 4099628.105799999, 4813627.897500001 4024026.3301, 4778123.9757 3992595.4799000006, 4756741.1951 4006531.7815000005, 4749146.8927 3979009.009299999, 4713515.568299999 3965892.4120000005, 4730318.3267 3916416.1548999995, 4715177.6598000005 3895576.2678999994, 4723660.3072999995 3846239.482000001, 4714642.3265 3797035.8910000008, 4734261.931299999 3762690.9342, 4722886.927300001 3713585.4924999997, 4707053.106899999 3735827.7872, 4695105.4978 3706695.4233999997, 4680618.7213 3681309.1801999994, 4604192.8281 3670893.6075, 4583909.419 3601419.1911999993, 4522235.599300001 3592091.9229000006, 4487078.975199999 3662743.1703999992, 4499886.534700001 3708681.501700001, 4436222.649900001 3830455.2589999996, 4409723.8868 3876749.5907000005, 4390494.7667 3950683.3049999997, 4390976.5208 3986335.1828000005, 4404885.393100001 3988539.145199999, 4414590.9651999995 3982028.8113, 4419716.5154 3995431.0604, 4425445.6281 4016571.0274, 4429455.153999999 4078125.6467000004, 4424393.606000001 4083582.6481999997, 4441629.048599999 4089343.866800001, 4457049.282199999 4110970.5056999996, 4462806.228700001 4150810.2381999996, 4445605.062000001 4211601.132300001, 4465658.2871 4219983.2985, 4465246.070800001 4261087.826400001, 4436644.1457 4298009.4877, 4440904.7279 4353715.4593, 4438332.4803 4360687.112199999, 4424849.4953000005 4454897.044, 4428899.1995 4481072.204600001, 4430966.837200001 4503388.899800001, 4445732.5723 4529630.7809, 4475502.457900001 4555685.7949, 4517888.839400001 4557693.2116, 4520389.6183 4592218.7552000005, 4506168.570599999 4609613.9451, 4500553.1686 4616548.5276, 4525407.6393 4674222.130000001, 4532037.6675 4779505.4033, 4566978.611199999 4813265.669600001, 4563730.3927 4830690.195, 4598950.251599999 4895824.906199999, 4587371.919 4935277.019400001, 4605710.551100001 4987904.661900001, 4626113.4443 5012633.2763, 4644414.573000001 5008079.9103, 4659061.4355999995 5021416.403899999, 4655620.2413 5065448.5865, 4731700.331700001 5058529.409600001, 4736996.603800001 5130193.0163, 4744757.5046 5136005.0243, 4882630.9618999995 5043779.6998, 4929425.7168000005 4919018.998299999, 4939457.887 4857278.8039, 4967895.5929000005 4811191.227299999, 4971226.650800001 4797934.918099999)))</t>
+  </si>
+  <si>
+    <t>1245, 1255, 1247</t>
+  </si>
+  <si>
+    <t>MULTIPOLYGON (((4983243.0832 4137834.6878999993, 4976174.6581999995 4151378.9044000003, 4992663.9954 4157357.0139000006, 5001266.190300001 4135605.8715000004, 4991593.5600000005 4121921.4332999997, 4983243.0832 4137834.6878999993)), ((4849742.4968 4160483.1746999994, 4852846.601299999 4171726.2469999995, 4880171.5502 4177511.1174999997, 4895042.2908 4177026.4817999993, 4906991.8747000005 4154328.9218000006, 4885222.891100001 4144299.7602999993, 4849742.4968 4160483.1746999994)), ((4912180.695800001 4177878.5001999997, 4916772.704299999 4207999.920399999, 4930820.4868 4199582.882300001, 4931862.395199999 4177670.5063000005, 4912180.695800001 4177878.5001999997)), ((5235584.481799999 4253987.700099999, 5218623.9695999995 4259109.271199999, 5072006.100400001 4157718.8603000008, 5046107.8858 4154066.092, 5041165.411 4175348.3124, 5018494.7948 4156322.9853000008, 4995850.579500001 4183128.9558000006, 4951957.2597 4163052.7992000002, 4928832.2377 4235378.977600001, 4936923.693700001 4266002.3083999995, 4936631.214199999 4321581.8928, 4914878.0491 4364837.4351, 4889603.577 4446256.645300001, 4885968.065099999 4486648.1655, 4960842.423900001 4587133.144400001, 4985007.287599999 4614223.249299999, 5005513.895300001 4674929.630000001, 5012198.095899999 4702483.2796, 5003689.2258 4735026.387800001, 5015892.637 4739799.261299999, 5026115.522500001 4715435.056299999, 5040402.866800001 4727558.8904, 5015509.8336 4795585.6214000005, 4994333.1877999995 4799920.049000001, 4967895.5929000005 4811191.227299999, 4939457.887 4857278.8039, 4929425.7168000005 4919018.998299999, 4882630.9618999995 5043779.6998, 4744757.5046 5136005.0243, 4760596.4999 5158082.832699999, 4770072.6545 5167675.498199999, 4781583.823799999 5166481.751, 4786541.835899999 5162420.5875, 4801469.590500001 5146847.401900001, 4853855.835899999 5111817.7235, 4889483.3258 5130749.9980999995, 4932226.6894000005 5124378.9022, 4948346.343599999 5164461.637800001, 4943807.892000001 5250194.7501, 4996322.788799999 5301735.9025, 5064258.8256 5266231.4595, 5072809.138800001 5205674.012399999, 5073953.327199999 5144644.1348, 5089249.3467999995 5117360.5407, 5102408.6712 5111127.675100001, 5162417.305299999 5069947.8796, 5150352.6445 4990509.077, 5179392.876800001 4947691.8651, 5187963.2129999995 4936693.889, 5232501.782500001 4872869.5013, 5227537.041200001 4839633.0667, 5244975.466499999 4776304.910700001, 5266351.009099999 4762868.237500001, 5273600.8697 4742689.323000001, 5277738.1303 4731171.742000001, 5306798.164799999 4707264.389699999, 5307643.1349 4671756.4691, 5296286.373299999 4657446.260399999, 5368495.0458 4621133.819499999, 5400404.300799999 4588601.680299999, 5398603.942600001 4540274.9559, 5368677.9329 4456900.7027, 5295069.118799999 4299085.5338, 5288693.066400001 4283533.598099999, 5273756.7454 4265294.494000001, 5235584.481799999 4253987.700099999)))</t>
+  </si>
+  <si>
+    <t>1315, 996, 1321, 1014</t>
+  </si>
+  <si>
+    <t>POLYGON ((5279162.0724 2843993.0884000007, 5232859.490499999 2796039.1740000006, 5229004.0033 2795171.6274999995, 5203937.8378 2726154.8417000007, 5193727.933599999 2682800.758199999, 5176556.373 2644649.0899, 5149175.4487 2633827.471999999, 5145578.1417 2620383.8599999994, 5112369.7859000005 2611777.776900001, 5102473.9651 2611270.4463, 5081487.072000001 2610251.4306000005, 5068153.706700001 2612699.3713000007, 5040491.776900001 2587133.3753999993, 5009623.0449 2575455.7397000007, 5004436.5659 2574073.972100001, 4935711.286699999 2552486.5812999997, 4914925.3323 2556676.2138, 4897745.692500001 2566288.3329000007, 4885838.4597 2569452.5403000005, 4850286.352600001 2603109.4586999994, 4848359.353399999 2606260.0957999993, 4827385.8894 2618351.326199999, 4807826.1532000005 2644113.7391999997, 4786947.8336 2658724.9250000007, 4811576.9648 2680342.3698999994, 4806751.430600001 2714374.6019, 4821838.7709 2726165.9716, 4802912.6987 2748897.5074000005, 4844980.647700001 2758836.3794, 4854633.2936 2791782.4586999994, 4861008.709100001 2793004.7731, 4897845.193 2768465.3463000003, 4912119.8091 2767793.6603999995, 4982212.621300001 2784591.9952000007, 4974418.3094 2794447.3637000006, 4985038.552200001 2811671.278999999, 4991117.540200001 2814757.4297, 5066406.101399999 2834643.9049999993, 5092186.1017 2871555.9102999996, 5159903.8344 2891350.2935000006, 5214660.069499999 2880853.8320000004, 5216710.2202 2884027.4801000003, 5279162.0724 2843993.0884000007))</t>
+  </si>
+  <si>
+    <t>POLYGON ((5202339.4189 3510354.4520999994, 5183759.5777 3540551.7379, 5147704.3763999995 3546424.1741000004, 5140298.2325 3597576.4493000004, 5120797.056700001 3621728.9948999994, 5059830.3111000005 3623763.2136000004, 5041850.8978 3630961.417300001, 5034954.090299999 3627178.4388999995, 5009299.3714000005 3698293.4141000006, 5007410.6272 3715789.812999999, 5057503.611199999 3759611.2509000003, 5097787.3825 3764687.1994000003, 5114449.1548999995 3771206.5187, 5130157.0145 3766126.4203999992, 5192242.198100001 3769546.0725, 5231736.936000001 3790696.4021000005, 5298223.159499999 3769132.5767, 5314580.0447 3760461.810900001, 5356923.878900001 3740090.5593, 5374609.0176 3696416.7972999997, 5371400.884400001 3683815.693499999, 5351501.5657 3675907.1116000004, 5347477.6841 3660179.2818, 5334161.9756000005 3651099.0450999998, 5326369.9383000005 3631446.2008999996, 5331054.435699999 3607861.5889999997, 5334687.998299999 3564716.6867999993, 5282724.105799999 3548285.2378000002, 5264627.805199999 3519688.9715, 5202339.4189 3510354.4520999994))</t>
+  </si>
+  <si>
+    <t>POLYGON ((3232232.5056999996 4908819.394200001, 3228233.5602 4870363.569599999, 3204109.8178000003 4833704.7827, 3134322.9992999993 4791820.6537999995, 2952145.4415000007 4768793.2086, 2869561.7916 4813198.1653, 2806151.7323000003 4886031.692, 2807712.9813 4905169.5998, 2838648.7873 4925562.6888999995, 2858074.2029 4922790.0057, 2829547.3879000004 4943649.892899999, 2812929.4616 4999239.850400001, 2865876.1325000003 5053660.294600001, 2823221.181 5079215.351, 2822380.9919000007 5107070.060799999, 2905636.1961000003 5139349.110200001, 2929483.0209 5108676.689099999, 2934492.6215000004 5028953.1491, 2992571.7792000007 5054149.333900001, 3105557.8594000004 5016973.5471, 3182248.6417999994 5029088.8411, 3215343.221000001 4973810.8059, 3232232.5056999996 4908819.394200001))</t>
+  </si>
+  <si>
+    <t>Reykjavik</t>
+  </si>
+  <si>
+    <t>1035, 1021, 1020, 1019, 1032, 1036</t>
+  </si>
+  <si>
+    <t>POLYGON ((5234032.6688 2964367.443499999, 5224941.452400001 2937247.0222999994, 5224306.5472 2918985.7387000006, 5215149.253900001 2903071.4311999995, 5216710.2202 2884027.4801000003, 5214660.069499999 2880853.8320000004, 5159903.8344 2891350.2935000006, 5092186.1017 2871555.9102999996, 5066406.101399999 2834643.9049999993, 4991117.540200001 2814757.4297, 4985038.552200001 2811671.278999999, 4974418.3094 2794447.3637000006, 4982212.621300001 2784591.9952000007, 4912119.8091 2767793.6603999995, 4897845.193 2768465.3463000003, 4861008.709100001 2793004.7731, 4854633.2936 2791782.4586999994, 4846489.8573 2803511.3914, 4839232.970000001 2808802.6084000003, 4827291.811899999 2837437.805400001, 4833565.827299999 2848880.935799999, 4832035.225400001 2857836.831599999, 4863380.6556 2882817.0767, 4881191.0218 2889219.8411999997, 4924768.599400001 2945551.253799999, 4929608.184 2955255.7161, 4960290.233100001 2972378.4113999996, 4981146.918199999 2964053.5408999994, 5003133.9341 2988592.054199999, 5038951.0986 2947340.4475, 5056054.9975000005 2957982.587099999, 5088278.376800001 2978299.3541, 5144084.4395 2988537.182600001, 5234032.6688 2964367.443499999))</t>
+  </si>
+  <si>
+    <t>1305, 1016, 1012, 1298, 1314, 1013</t>
+  </si>
+  <si>
+    <t>POLYGON ((5279162.0724 2843993.0884000007, 5295136.3665 2864796.5406, 5322716.993799999 2853435.5439999998, 5401520.148 2864803.687999999, 5434196.9673 2848154.7302, 5512616.740900001 2893427.4849999994, 5544403.6996 2932763.283, 5593798.1768 2903635.9738999996, 5616141.5503 2872864.2773, 5688359.5791 2804383.0753000006, 5707261.7586 2763100.8388, 5707440.4903 2725187.3452000003, 5731142.557600001 2657535.0019000005, 5770137.441400001 2642596.7248, 5814677.389 2672729.356899999, 5845263.706700001 2669525.889799999, 5848989.4395 2658978.6268000007, 5849006.036699999 2619962.917300001, 5811317.4219 2587520.1794000007, 5797648.9791 2549192.7453000005, 5803878.310699999 2477397.2667999994, 5728800.2762 2487225.7224000003, 5692416.938200001 2494414.3203999996, 5625117.978399999 2468918.4036, 5623303.4111 2468347.4583, 5577228.5008000005 2418572.3232000005, 5568140.8038 2411494.9099000003, 5548282.5320999995 2408758.8222000003, 5496185.8872 2405891.3795999996, 5470511.1852 2397911.185900001, 5453726.007200001 2394931.2346, 5413836.1129 2397732.036699999, 5375819.819 2393236.6164999995, 5363358.685799999 2390534.4637, 5355670.479599999 2421937.2738000005, 5330611.946599999 2430822.4794999994, 5309847.146500001 2471925.0744000003, 5272190.4103 2464260.9650999997, 5271841.4077 2464554.9574999996, 5217048.233999999 2480557.5320999995, 5220467.4044 2522847.3762999997, 5182474.6197 2531852.3934000004, 5147917.9965 2579517.2293, 5112369.7859000005 2611777.776900001, 5145578.1417 2620383.8599999994, 5149175.4487 2633827.471999999, 5176556.373 2644649.0899, 5193727.933599999 2682800.758199999, 5203937.8378 2726154.8417000007, 5229004.0033 2795171.6274999995, 5232859.490499999 2796039.1740000006, 5279162.0724 2843993.0884000007))</t>
+  </si>
+  <si>
+    <t>POLYGON ((4786947.8336 2658724.9250000007, 4807826.1532000005 2644113.7391999997, 4827385.8894 2618351.326199999, 4800109.809699999 2617566.9919000007, 4805669.1493 2605574.086100001, 4773662.2333 2591913.8157, 4767522.000399999 2589203.2477, 4756287.5679 2569024.9848999996, 4763299.947699999 2557231.321799999, 4741351.1735 2535261.6369000003, 4735901.171599999 2531543.4870999996, 4730255.16 2493771.1679, 4677333.5853 2517639.023499999, 4664447.307399999 2498010.1328999996, 4643271.7804000005 2494333.5858999994, 4642725.0929000005 2494425.2696, 4606910.833699999 2489415.437000001, 4611706.6953 2505312.588199999, 4620627.842700001 2504937.5133999996, 4625607.4045 2510559.301999999, 4615786.936899999 2521947.978599999, 4600790.590299999 2528446.5233999994, 4600801.203500001 2529734.6720000003, 4591854.307499999 2555074.1741000004, 4591448.658299999 2588075.378900001, 4604291.080700001 2598604.5420999993, 4606152.070499999 2608175.0654000007, 4661893.2820999995 2602363.9946, 4672386.9882 2595156.8956000004, 4680269.760500001 2604354.046, 4708765.1296999995 2628648.7771000005, 4734492.067299999 2630626.1513, 4753009.4882 2637824.3693000004, 4763403.3181 2638817.9725, 4778298.5133 2654263.0853000004, 4786947.8336 2658724.9250000007))</t>
+  </si>
+  <si>
+    <t>1319, 1318, 1310, 1311, 688</t>
+  </si>
+  <si>
+    <t>MULTIPOLYGON (((4826233.6381 2163733.9481000006, 4836438.4728 2175422.445800001, 4857612.1327 2174401.204500001, 4868898.306299999 2156198.854800001, 4844342.796700001 2151647.2257000003, 4826233.6381 2163733.9481000006)), ((4766842.662799999 2225617.5578000005, 4774199.7623 2232729.043400001, 4799661.0633000005 2245651.5637, 4812172.5887 2241080.588300001, 4802010.203199999 2225569.772, 4783944.4416000005 2217553.4005999994, 4766842.662799999 2225617.5578000005)), ((4892341.0188 2221845.6352999993, 4886810.7552000005 2231551.929199999, 4894495.299699999 2246522.1159000006, 4909039.6316 2248927.944, 4919648.4245 2235888.4771, 4916831.1713 2223445.9471000005, 4892341.0188 2221845.6352999993)), ((5009325.8891 2474681.6164999995, 4991980.3915 2480137.603599999, 4951514.7261 2480303.1921999995, 4937776.332599999 2471262.3274000008, 4906108.8029 2478963.5726999994, 4882408.3431 2477037.91, 4813686.818299999 2460179.387599999, 4779874.8684 2474907.3243000004, 4774121.292099999 2442304.3264000006, 4809434.5459 2391562.4036, 4814757.7227 2364694.1284999996, 4837474.2413 2348050.0409999993, 4846574.346000001 2341238.2278000005, 4927371.7873 2260004.8387, 4989825.736199999 2212174.6248000003, 5014573.7599 2200024.6327, 5023279.372199999 2185927.997300001, 4972072.864700001 2210100.3878000006, 4946488.074999999 2229853.1834999993, 4940446.4383000005 2234753.4148999993, 4920627.898499999 2249010.5722000003, 4884345.8248 2273303.3604000006, 4808250.023800001 2285465.8763999995, 4766932.5394 2321857.4737, 4749009.876599999 2330506.2741, 4749260.9528 2326768.6240999997, 4749291.721999999 2326310.4782999996, 4749538.3462000005 2322637.5369000006, 4749569.6373 2322171.4230000004, 4749610.4487 2321563.4612000007, 4749742.0262 2319603.1128000002, 4749967.016899999 2316250.1043999996, 4750169.0184 2313238.717, 4741377.6719 2321524.0523000006, 4724762.7117 2349761.401799999, 4742242.8968 2376582.9690000005, 4715103.4088 2395120.4186000004, 4710045.4332 2410424.7612999994, 4706013.147500001 2448078.6213000007, 4678709.635 2434724.932600001, 4653693.8279 2458516.5646, 4625173.1523 2427475.9804999996, 4599008.8037 2476415.494000001, 4606910.833699999 2489415.437000001, 4642725.0929000005 2494425.2696, 4643271.7804000005 2494333.5858999994, 4664447.307399999 2498010.1328999996, 4677333.5853 2517639.023499999, 4730255.16 2493771.1679, 4735901.171599999 2531543.4870999996, 4741351.1735 2535261.6369000003, 4763299.947699999 2557231.321799999, 4756287.5679 2569024.9848999996, 4767522.000399999 2589203.2477, 4773662.2333 2591913.8157, 4805669.1493 2605574.086100001, 4800109.809699999 2617566.9919000007, 4827385.8894 2618351.326199999, 4848359.353399999 2606260.0957999993, 4850286.352600001 2603109.4586999994, 4885838.4597 2569452.5403000005, 4897745.692500001 2566288.3329000007, 4914925.3323 2556676.2138, 4935711.286699999 2552486.5812999997, 5004436.5659 2574073.972100001, 5009623.0449 2575455.7397000007, 5026320.3224 2528866.5682999995, 5024761.136399999 2522836.0852000006, 5031555.451400001 2513131.0206000004, 5060947.4131000005 2497458.0582999997, 5039110.455499999 2489241.2667999994, 5033462.4998 2459084.4516000003, 5018480.271600001 2458933.7032999992, 5009325.8891 2474681.6164999995)))</t>
+  </si>
+  <si>
+    <t>681, 1291, 1292, 1293</t>
+  </si>
+  <si>
+    <t>Türkiye</t>
+  </si>
+  <si>
+    <t>MULTIPOLYGON (((5665548.799000001 2021393.5497999992, 5647895.333699999 2032533.9031000007, 5678158.2907 2059036.8673999999, 5686401.606799999 2038433.7096999995, 5665548.799000001 2021393.5497999992)), ((6971457.456800001 2641629.5605999995, 7039843.9048999995 2620996.2040999997, 7042456.9915 2614067.5738999993, 7072348.187899999 2593859.6841, 7097392.381899999 2525649.5086000003, 7157971.4132 2539552.8128999993, 7200768.670700001 2525292.1191000007, 7207824.4076000005 2518558.9759, 7180384.485200001 2515331.3751999997, 7182389.863500001 2483234.6312000006, 7161574.8838 2461759.922700001, 7236798.2401 2366482.6076999996, 7242714.932399999 2323929.8709999993, 7262037.1986 2318390.437000001, 7293423.442 2286500.9360000007, 7315862.6073 2266543.1262, 7283937.5315000005 2233986.6587000005, 7258803.624500001 2250900.5209999997, 7202815.5611000005 2223242.4891999997, 7154667.656300001 2212020.4042000007, 7124012.305400001 2165629.3127999995, 7103113.676200001 2171297.1703999992, 7068256.7217 2139622.1384999994, 6995339.5594 2106571.0227000006, 6958937.7105 2067415.2199000008, 6884158.5572 2009049.2844999991, 6780983.347200001 1988231.3523999993, 6747420.0195 1958428.3577999994, 6712732.7217999995 1942071.8383000009, 6667078.8047 1943517.4802, 6665485.5601 1942998.0375999995, 6680951.7039 1881483.8074999992, 6658440.251700001 1827795.3937, 6632484.1888 1824591.7613999993, 6613549.9582 1863788.5624000002, 6629679.3904 1913288.8247999996, 6604629.318299999 1929139.0099, 6573381.1 1879906.4305000007, 6520092.964299999 1880306.4375, 6475379.6327 1850275.8661000002, 6428168.735400001 1781893.5724999998, 6340388.0031 1747312.3746000007, 6263190.4365 1781527.7017, 6170186.3872 1785985.0524000004, 6153377.519099999 1775001.0872000009, 6143638.330600001 1714866.6030000001, 6095150.044600001 1686268.1022999994, 6046336.5285 1688777.9886000007, 5969219.4427000005 1726746.1736999992, 5921216.427100001 1702196.0600000005, 5917612.034600001 1728639.5223999992, 5867935.2455 1731734.0724999998, 5859174.7631 1770511.9892999995, 5843580.828400001 1775482.7113000005, 5836588.2962 1816074.271400001, 5758196.4399 1845969.5074000005, 5780870.9004 1907184.6307999995, 5765133.607899999 1947264.7561000008, 5760725.334899999 1983691.8000000007, 5744714.005999999 1984964.8693000004, 5715425.365499999 1972078.1105000004, 5701751.8212 1984521.3738000002, 5693475.3555 2016894.168299999, 5706752.212300001 2067184.2843999993, 5801743.3506000005 2084104.5943999998, 5854053.862500001 2107095.8665999994, 5910777.8969 2119687.5295, 5920390.886499999 2131891.8538000006, 5917207.304300001 2145272.4524000008, 5959377.2969 2169198.0484999996, 5940443.759199999 2176264.6207, 5903691.669 2182081.2392999995, 5912477.327 2219090.911699999, 5974176.278899999 2223871.1973, 6012649.8224 2239140.841600001, 6066415.911900001 2241475.3683, 6090470.8893 2253507.5096000005, 6138406.577299999 2321627.943600001, 6164277.663899999 2347358.2804000005, 6183748.3344 2366948.9923, 6228777.543500001 2399837.196900001, 6297883.448899999 2416571.0295, 6356465.817399999 2443434.8202, 6395523.5098 2424239.2030999996, 6409166.8167 2417609.2498000003, 6440997.9889 2436614.3001000006, 6484464.5649999995 2407241.4979, 6518512.2499 2422758.3924000002, 6554504.056 2413417.5238000005, 6636245.636299999 2422566.8159999996, 6714844.6566 2468396.6492, 6806797.9845 2496974.0232999995, 6863319.487 2563702.9341, 6877693.0627999995 2593564.760399999, 6954095.9932 2618883.6136000007, 6971457.456800001 2641629.5605999995)), ((5687246.9263 2242311.344799999, 5716919.9485 2257473.069700001, 5723794.925799999 2269102.7313, 5804912.6646 2276442.7947000004, 5816890.4836 2250802.4026999995, 5824292.444399999 2234996.306500001, 5826981.3456999995 2233956.2378000002, 5888007.035499999 2217366.2183999997, 5895969.377699999 2183332.2357, 5824749.2566 2171034.837200001, 5791286.5868999995 2156409.0371000003, 5751528.5013 2100720.0274, 5730188.575300001 2106048.3146, 5670221.351600001 2102712.0823, 5701097.2457 2187851.018100001, 5675518.538699999 2215228.6450999994, 5687246.9263 2242311.344799999)))</t>
+  </si>
+  <si>
+    <t>1070, 1066, 1059, 1026, 1017, 1015, 1012, 1018</t>
+  </si>
+  <si>
+    <t>POLYGON ((6405736.0385 3072353.5945999995, 6173692.2521 2869322.7239999995, 6186373.021299999 2843117.8007999994, 6257307.7173 2805770.4575999994, 6326128.088099999 2841270.715, 6347602.0151 2828470.3323, 6343361.379000001 2805148.6952, 6288142.2095 2779496.880999999, 6210473.112 2689790.656300001, 6171197.9552 2673707.5195000004, 6138982.3398 2727478.769200001, 6070957.064099999 2749387.8871999998, 6097527.474300001 2827176.1456000004, 5990357.861500001 2815842.1019, 5979076.2434 2858227.0118000004, 5909836.589400001 2831489.0457000006, 5853233.531400001 2715737.3955000006, 5845263.706700001 2669525.889799999, 5814677.389 2672729.356899999, 5770137.441400001 2642596.7248, 5731142.557600001 2657535.0019000005, 5759638.049799999 2705422.9974000007, 5774080.005000001 2741552.1723999996, 5765467.1536 2779701.1078999992, 5828338.604900001 2794310.7913000006, 5830471.3160999995 2815727.8868000004, 5779911.647600001 2884071.8792000003, 5752297.176100001 2894592.8528000005, 5738508.6105 2940292.4295000006, 5716681.169500001 2943897.9199, 5700375.4475 2956825.4333999995, 5610348.151799999 2971985.3390999995, 5544403.6996 2932763.283, 5512616.740900001 2893427.4849999994, 5434196.9673 2848154.7302, 5401520.148 2864803.687999999, 5322716.993799999 2853435.5439999998, 5295136.3665 2864796.5406, 5279162.0724 2843993.0884000007, 5216710.2202 2884027.4801000003, 5215149.253900001 2903071.4311999995, 5224306.5472 2918985.7387000006, 5224941.452400001 2937247.0222999994, 5234032.6688 2964367.443499999, 5242087.6472 2978646.089400001, 5233492.579700001 3019106.4867000002, 5280978.566199999 3104580.3881, 5311677.2048 3151424.7452000007, 5271129.0626 3219181.101500001, 5260075.682 3243410.1711, 5309900.3697 3294184.1675000004, 5367193.8565 3314815.0901999995, 5489601.131999999 3320921.044399999, 5539611.837099999 3305695.2524999995, 5568486.086999999 3326331.3630999997, 5609105.198000001 3312077.5097000003, 5623484.6787 3338741.5080999993, 5649322.578500001 3323500.0744000003, 5697532.5516 3344818.5868999995, 5729662.489600001 3335175.8210000005, 5722651.774499999 3373609.860200001, 5733570.6416 3417705.5022, 5787847.8748 3444371.5252, 5909220.519200001 3506330.8147, 5963853.179400001 3467501.895300001, 5975902.8859 3424733.5331999995, 6042081.355799999 3414095.7375000007, 6103993.9792 3350426.8977000006, 6167588.9081 3357064.7671000008, 6217164.906199999 3392347.9354999997, 6273452.930600001 3366807.8874999993, 6353898.8817 3383094.6689, 6421947.966 3373293.446900001, 6441278.664999999 3350232.974199999, 6439067.2498 3297281.8641, 6468536.5111 3244905.4944, 6477226.2146000005 3200257.0533000007, 6406314.081499999 3140118.3693000004, 6405736.0385 3072353.5945999995))</t>
+  </si>
+  <si>
+    <t>POLYGON ((5707440.4903 2725187.3452000003, 5707261.7586 2763100.8388, 5688359.5791 2804383.0753000006, 5616141.5503 2872864.2773, 5593798.1768 2903635.9738999996, 5544403.6996 2932763.283, 5610348.151799999 2971985.3390999995, 5700375.4475 2956825.4333999995, 5716681.169500001 2943897.9199, 5738508.6105 2940292.4295000006, 5752297.176100001 2894592.8528000005, 5779911.647600001 2884071.8792000003, 5830471.3160999995 2815727.8868000004, 5828338.604900001 2794310.7913000006, 5765467.1536 2779701.1078999992, 5774080.005000001 2741552.1723999996, 5759638.049799999 2705422.9974000007, 5731142.557600001 2657535.0019000005, 5707440.4903 2725187.3452000003))</t>
+  </si>
+  <si>
+    <t>1254, 1247, 1232</t>
   </si>
 </sst>
 </file>
@@ -3172,7 +3355,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3364,6 +3547,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="10">
     <border>
@@ -3525,11 +3714,12 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -3851,18 +4041,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H241"/>
+  <dimension ref="A1:M241"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="50.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20.42578125" customWidth="1"/>
     <col min="4" max="4" width="31.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="22.28515625" customWidth="1"/>
     <col min="7" max="7" width="25.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="30.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="30.7109375" customWidth="1"/>
+    <col min="10" max="10" width="33.7109375" customWidth="1"/>
+    <col min="11" max="11" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3879,16 +4074,28 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>975</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>987</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>977</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="K1" s="1" t="s">
+        <v>982</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -3905,7 +4112,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -3922,7 +4129,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -3939,7 +4146,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -3956,7 +4163,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -3973,7 +4180,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>28</v>
       </c>
@@ -3990,13 +4197,13 @@
         <v>31</v>
       </c>
       <c r="F7" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="G7" t="s">
-        <v>971</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>32</v>
       </c>
@@ -4013,7 +4220,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>36</v>
       </c>
@@ -4030,7 +4237,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>41</v>
       </c>
@@ -4047,7 +4254,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>45</v>
       </c>
@@ -4061,7 +4268,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>49</v>
       </c>
@@ -4078,7 +4285,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>53</v>
       </c>
@@ -4095,31 +4302,39 @@
         <v>57</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
+    <row r="14" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E14" s="3" t="s">
+      <c r="D14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>970</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>975</v>
-      </c>
-      <c r="H14" s="3"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F14" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>973</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>969</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>62</v>
       </c>
@@ -4136,7 +4351,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>66</v>
       </c>
@@ -4153,7 +4368,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>71</v>
       </c>
@@ -4170,30 +4385,30 @@
         <v>74</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+    <row r="18" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="D18" t="s">
-        <v>9</v>
-      </c>
-      <c r="E18" t="s">
+      <c r="D18" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E18" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F18" s="4" t="s">
+        <v>968</v>
+      </c>
+      <c r="G18" s="4" t="s">
         <v>970</v>
       </c>
-      <c r="G18" t="s">
-        <v>972</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>79</v>
       </c>
@@ -4210,7 +4425,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>83</v>
       </c>
@@ -4227,30 +4442,39 @@
         <v>86</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+    <row r="21" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D21" t="s">
-        <v>9</v>
-      </c>
-      <c r="E21" t="s">
+      <c r="D21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="F21" t="s">
-        <v>970</v>
-      </c>
-      <c r="G21" t="s">
-        <v>970</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F21" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>969</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>91</v>
       </c>
@@ -4267,30 +4491,33 @@
         <v>94</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+    <row r="23" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="D23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E23" t="s">
+      <c r="D23" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E23" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="F23" t="s">
-        <v>970</v>
-      </c>
-      <c r="G23" t="s">
-        <v>971</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F23" s="3" t="s">
+        <v>968</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>1025</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>99</v>
       </c>
@@ -4307,7 +4534,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>103</v>
       </c>
@@ -4324,7 +4551,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>107</v>
       </c>
@@ -4341,7 +4568,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>112</v>
       </c>
@@ -4358,7 +4585,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>116</v>
       </c>
@@ -4375,7 +4602,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>120</v>
       </c>
@@ -4392,7 +4619,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>124</v>
       </c>
@@ -4409,7 +4636,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>128</v>
       </c>
@@ -4426,7 +4653,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>132</v>
       </c>
@@ -4443,7 +4670,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>137</v>
       </c>
@@ -4460,30 +4687,39 @@
         <v>140</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+    <row r="34" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C34" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="D34" t="s">
-        <v>9</v>
-      </c>
-      <c r="E34" t="s">
+      <c r="D34" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E34" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="F34" t="s">
-        <v>970</v>
-      </c>
-      <c r="G34" t="s">
-        <v>970</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F34" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>969</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>969</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="J34" s="2" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>145</v>
       </c>
@@ -4500,7 +4736,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>149</v>
       </c>
@@ -4517,7 +4753,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>153</v>
       </c>
@@ -4534,7 +4770,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>157</v>
       </c>
@@ -4551,7 +4787,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>161</v>
       </c>
@@ -4568,7 +4804,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>165</v>
       </c>
@@ -4585,35 +4821,44 @@
         <v>168</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
+    <row r="41" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C41" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="D41" t="s">
-        <v>9</v>
-      </c>
-      <c r="E41" t="s">
+      <c r="D41" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E41" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="F41" t="s">
-        <v>970</v>
-      </c>
-      <c r="G41" t="s">
-        <v>971</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F41" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>993</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>969</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="J41" s="2" t="s">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>173</v>
       </c>
       <c r="B42" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="C42" t="s">
         <v>174</v>
@@ -4625,7 +4870,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>176</v>
       </c>
@@ -4642,7 +4887,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>181</v>
       </c>
@@ -4659,7 +4904,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>185</v>
       </c>
@@ -4676,7 +4921,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>189</v>
       </c>
@@ -4692,8 +4937,9 @@
       <c r="E46" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="M46" s="1"/>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>193</v>
       </c>
@@ -4710,7 +4956,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>197</v>
       </c>
@@ -4727,7 +4973,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>201</v>
       </c>
@@ -4744,7 +4990,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>205</v>
       </c>
@@ -4761,7 +5007,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>209</v>
       </c>
@@ -4778,7 +5024,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>212</v>
       </c>
@@ -4795,7 +5041,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>216</v>
       </c>
@@ -4812,47 +5058,71 @@
         <v>219</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
+    <row r="54" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="C54" t="s">
+      <c r="C54" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="D54" t="s">
-        <v>9</v>
-      </c>
-      <c r="E54" t="s">
+      <c r="D54" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E54" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="F54" t="s">
-        <v>970</v>
-      </c>
-      <c r="G54" t="s">
-        <v>971</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
+      <c r="F54" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="G54" s="2">
+        <v>1024</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>969</v>
+      </c>
+      <c r="I54" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="J54" s="2" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B55" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="C55" t="s">
+      <c r="C55" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="D55" t="s">
-        <v>9</v>
-      </c>
-      <c r="E55" t="s">
+      <c r="D55" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E55" s="2" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F55" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>999</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>969</v>
+      </c>
+      <c r="I55" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="J55" s="2" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>228</v>
       </c>
@@ -4869,24 +5139,39 @@
         <v>229</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
+    <row r="57" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B57" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="C57" t="s">
+      <c r="C57" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="D57" t="s">
-        <v>9</v>
-      </c>
-      <c r="E57" t="s">
+      <c r="D57" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E57" s="2" t="s">
         <v>234</v>
       </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F57" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>1002</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>969</v>
+      </c>
+      <c r="I57" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="J57" s="2" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>235</v>
       </c>
@@ -4903,7 +5188,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>239</v>
       </c>
@@ -4920,7 +5205,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>243</v>
       </c>
@@ -4937,7 +5222,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>247</v>
       </c>
@@ -4954,24 +5239,39 @@
         <v>250</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
+    <row r="62" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B62" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="C62" t="s">
+      <c r="C62" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="D62" t="s">
-        <v>9</v>
-      </c>
-      <c r="E62" t="s">
+      <c r="D62" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E62" s="2" t="s">
         <v>254</v>
       </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F62" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>969</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>969</v>
+      </c>
+      <c r="I62" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="J62" s="2" t="s">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>255</v>
       </c>
@@ -4988,7 +5288,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>259</v>
       </c>
@@ -5005,7 +5305,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>264</v>
       </c>
@@ -5022,7 +5322,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>268</v>
       </c>
@@ -5039,7 +5339,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>272</v>
       </c>
@@ -5056,13 +5356,28 @@
         <v>275</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>973</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+        <v>971</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="I67" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="J67" s="2" t="s">
+        <v>985</v>
+      </c>
+      <c r="K67" s="2" t="s">
+        <v>984</v>
+      </c>
+      <c r="L67" s="2" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>276</v>
       </c>
@@ -5079,24 +5394,39 @@
         <v>279</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
+    <row r="69" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B69" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="C69" t="s">
+      <c r="C69" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="D69" t="s">
-        <v>9</v>
-      </c>
-      <c r="E69" t="s">
+      <c r="D69" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E69" s="2" t="s">
         <v>283</v>
       </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F69" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>1011</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>969</v>
+      </c>
+      <c r="I69" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="J69" s="2" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>284</v>
       </c>
@@ -5113,7 +5443,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>288</v>
       </c>
@@ -5130,7 +5460,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>293</v>
       </c>
@@ -5147,7 +5477,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>297</v>
       </c>
@@ -5164,33 +5494,45 @@
         <v>301</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" s="3" t="s">
+    <row r="74" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="B74" s="3" t="s">
+      <c r="B74" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="C74" s="3" t="s">
+      <c r="C74" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="D74" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E74" s="3" t="s">
+      <c r="D74" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E74" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="F74" s="3" t="s">
-        <v>970</v>
-      </c>
-      <c r="G74" s="3" t="s">
-        <v>974</v>
-      </c>
-      <c r="H74" s="3" t="s">
-        <v>978</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F74" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>972</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>976</v>
+      </c>
+      <c r="I74" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="J74" s="2" t="s">
+        <v>990</v>
+      </c>
+      <c r="K74" s="2" t="s">
+        <v>988</v>
+      </c>
+      <c r="L74" s="2" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>306</v>
       </c>
@@ -5207,7 +5549,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>312</v>
       </c>
@@ -5224,7 +5566,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>316</v>
       </c>
@@ -5241,7 +5583,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>320</v>
       </c>
@@ -5258,7 +5600,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>324</v>
       </c>
@@ -5275,7 +5617,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>329</v>
       </c>
@@ -5292,7 +5634,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>333</v>
       </c>
@@ -5309,7 +5651,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>336</v>
       </c>
@@ -5326,7 +5668,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>341</v>
       </c>
@@ -5343,7 +5685,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>345</v>
       </c>
@@ -5360,7 +5702,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>349</v>
       </c>
@@ -5377,7 +5719,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>353</v>
       </c>
@@ -5394,24 +5736,24 @@
         <v>356</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
+    <row r="87" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="4" t="s">
         <v>357</v>
       </c>
-      <c r="B87" t="s">
+      <c r="B87" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="C87" t="s">
+      <c r="C87" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="D87" t="s">
-        <v>9</v>
-      </c>
-      <c r="E87" t="s">
+      <c r="D87" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E87" s="4" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>358</v>
       </c>
@@ -5428,7 +5770,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>361</v>
       </c>
@@ -5445,7 +5787,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>365</v>
       </c>
@@ -5462,7 +5804,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>369</v>
       </c>
@@ -5479,7 +5821,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>373</v>
       </c>
@@ -5496,7 +5838,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>377</v>
       </c>
@@ -5513,24 +5855,39 @@
         <v>380</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
+    <row r="94" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="B94" t="s">
+      <c r="B94" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="C94" t="s">
+      <c r="C94" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="D94" t="s">
-        <v>9</v>
-      </c>
-      <c r="E94" t="s">
+      <c r="D94" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E94" s="2" t="s">
         <v>384</v>
       </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F94" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="G94" s="2" t="s">
+        <v>1023</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>969</v>
+      </c>
+      <c r="I94" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="J94" s="2" t="s">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>385</v>
       </c>
@@ -5547,24 +5904,39 @@
         <v>388</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
+    <row r="96" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="B96" t="s">
+      <c r="B96" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="C96" t="s">
+      <c r="C96" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="D96" t="s">
-        <v>9</v>
-      </c>
-      <c r="E96" t="s">
+      <c r="D96" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E96" s="2" t="s">
         <v>392</v>
       </c>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F96" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="G96" s="2" t="s">
+        <v>1013</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>969</v>
+      </c>
+      <c r="I96" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="J96" s="2" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>393</v>
       </c>
@@ -5581,24 +5953,39 @@
         <v>396</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
+    <row r="98" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="B98" t="s">
+      <c r="B98" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="C98" t="s">
+      <c r="C98" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="D98" t="s">
-        <v>9</v>
-      </c>
-      <c r="E98" t="s">
+      <c r="D98" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E98" s="2" t="s">
         <v>400</v>
       </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F98" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="G98" s="2" t="s">
+        <v>969</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>969</v>
+      </c>
+      <c r="I98" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="J98" s="2" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>401</v>
       </c>
@@ -5615,7 +6002,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>405</v>
       </c>
@@ -5632,7 +6019,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>410</v>
       </c>
@@ -5649,7 +6036,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>414</v>
       </c>
@@ -5666,7 +6053,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>418</v>
       </c>
@@ -5683,2362 +6070,2599 @@
         <v>421</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
+    <row r="104" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="2" t="s">
         <v>422</v>
       </c>
-      <c r="B104" t="s">
+      <c r="B104" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="C104" t="s">
+      <c r="C104" s="2" t="s">
         <v>424</v>
       </c>
-      <c r="D104" t="s">
-        <v>9</v>
-      </c>
-      <c r="E104" t="s">
+      <c r="D104" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>1017</v>
+      </c>
+      <c r="F104" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="G104" s="2" t="s">
+        <v>969</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>969</v>
+      </c>
+      <c r="I104" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="J104" s="2" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="2" t="s">
         <v>425</v>
       </c>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A105" s="2" t="s">
+      <c r="B105" s="2" t="s">
         <v>426</v>
       </c>
-      <c r="B105" s="2" t="s">
+      <c r="C105" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="C105" s="2" t="s">
+      <c r="D105" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E105" s="2" t="s">
         <v>428</v>
       </c>
-      <c r="D105" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E105" s="2" t="s">
-        <v>429</v>
-      </c>
       <c r="F105" s="2" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="G105" s="2">
         <v>1320</v>
       </c>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H105" s="2" t="s">
+        <v>969</v>
+      </c>
+      <c r="I105" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="J105" s="2" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
+        <v>430</v>
+      </c>
+      <c r="B106" t="s">
         <v>431</v>
       </c>
-      <c r="B106" t="s">
+      <c r="C106" t="s">
         <v>432</v>
-      </c>
-      <c r="C106" t="s">
-        <v>433</v>
       </c>
       <c r="D106" t="s">
         <v>327</v>
       </c>
       <c r="E106" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
         <v>434</v>
       </c>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A107" t="s">
+      <c r="B107" t="s">
+        <v>429</v>
+      </c>
+      <c r="C107" t="s">
         <v>435</v>
       </c>
-      <c r="B107" t="s">
-        <v>430</v>
-      </c>
-      <c r="C107" t="s">
+      <c r="D107" t="s">
+        <v>9</v>
+      </c>
+      <c r="E107" t="s">
         <v>436</v>
       </c>
-      <c r="D107" t="s">
-        <v>9</v>
-      </c>
-      <c r="E107" t="s">
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
         <v>437</v>
       </c>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A108" t="s">
+      <c r="B108" t="s">
         <v>438</v>
       </c>
-      <c r="B108" t="s">
+      <c r="C108" t="s">
         <v>439</v>
       </c>
-      <c r="C108" t="s">
+      <c r="D108" t="s">
+        <v>9</v>
+      </c>
+      <c r="E108" t="s">
         <v>440</v>
       </c>
-      <c r="D108" t="s">
-        <v>9</v>
-      </c>
-      <c r="E108" t="s">
+    </row>
+    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
         <v>441</v>
       </c>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A109" t="s">
+      <c r="B109" t="s">
         <v>442</v>
       </c>
-      <c r="B109" t="s">
+      <c r="C109" t="s">
         <v>443</v>
       </c>
-      <c r="C109" t="s">
+      <c r="D109" t="s">
+        <v>9</v>
+      </c>
+      <c r="E109" t="s">
         <v>444</v>
       </c>
-      <c r="D109" t="s">
-        <v>9</v>
-      </c>
-      <c r="E109" t="s">
+    </row>
+    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A110" t="s">
+      <c r="B110" t="s">
         <v>446</v>
       </c>
-      <c r="B110" t="s">
+      <c r="C110" t="s">
         <v>447</v>
       </c>
-      <c r="C110" t="s">
+      <c r="D110" t="s">
+        <v>9</v>
+      </c>
+      <c r="E110" t="s">
         <v>448</v>
       </c>
-      <c r="D110" t="s">
-        <v>9</v>
-      </c>
-      <c r="E110" t="s">
+    </row>
+    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
         <v>449</v>
       </c>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A111" t="s">
+      <c r="B111" t="s">
         <v>450</v>
       </c>
-      <c r="B111" t="s">
+      <c r="C111" t="s">
         <v>451</v>
       </c>
-      <c r="C111" t="s">
+      <c r="D111" t="s">
+        <v>9</v>
+      </c>
+      <c r="E111" t="s">
         <v>452</v>
       </c>
-      <c r="D111" t="s">
-        <v>9</v>
-      </c>
-      <c r="E111" t="s">
+    </row>
+    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
         <v>453</v>
       </c>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A112" t="s">
+      <c r="B112" t="s">
         <v>454</v>
       </c>
-      <c r="B112" t="s">
+      <c r="C112" t="s">
         <v>455</v>
       </c>
-      <c r="C112" t="s">
+      <c r="D112" t="s">
+        <v>9</v>
+      </c>
+      <c r="E112" t="s">
         <v>456</v>
       </c>
-      <c r="D112" t="s">
-        <v>9</v>
-      </c>
-      <c r="E112" t="s">
+    </row>
+    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
         <v>457</v>
       </c>
-    </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A113" t="s">
+      <c r="B113" t="s">
         <v>458</v>
       </c>
-      <c r="B113" t="s">
+      <c r="C113" t="s">
         <v>459</v>
       </c>
-      <c r="C113" t="s">
+      <c r="D113" t="s">
+        <v>9</v>
+      </c>
+      <c r="E113" t="s">
         <v>460</v>
       </c>
-      <c r="D113" t="s">
-        <v>9</v>
-      </c>
-      <c r="E113" t="s">
+    </row>
+    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
         <v>461</v>
       </c>
-    </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A114" t="s">
+      <c r="B114" t="s">
         <v>462</v>
       </c>
-      <c r="B114" t="s">
+      <c r="C114" t="s">
         <v>463</v>
       </c>
-      <c r="C114" t="s">
+      <c r="D114" t="s">
+        <v>9</v>
+      </c>
+      <c r="E114" t="s">
         <v>464</v>
       </c>
-      <c r="D114" t="s">
-        <v>9</v>
-      </c>
-      <c r="E114" t="s">
+    </row>
+    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
         <v>465</v>
       </c>
-    </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A115" t="s">
+      <c r="B115" t="s">
         <v>466</v>
       </c>
-      <c r="B115" t="s">
+      <c r="C115" t="s">
         <v>467</v>
       </c>
-      <c r="C115" t="s">
+      <c r="D115" t="s">
+        <v>9</v>
+      </c>
+      <c r="E115" t="s">
         <v>468</v>
       </c>
-      <c r="D115" t="s">
-        <v>9</v>
-      </c>
-      <c r="E115" t="s">
+    </row>
+    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
         <v>469</v>
       </c>
-    </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A116" t="s">
+      <c r="B116" t="s">
         <v>470</v>
       </c>
-      <c r="B116" t="s">
+      <c r="C116" t="s">
         <v>471</v>
       </c>
-      <c r="C116" t="s">
+      <c r="D116" t="s">
+        <v>9</v>
+      </c>
+      <c r="E116" t="s">
         <v>472</v>
       </c>
-      <c r="D116" t="s">
-        <v>9</v>
-      </c>
-      <c r="E116" t="s">
+    </row>
+    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
         <v>473</v>
       </c>
-    </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A117" t="s">
+      <c r="B117" t="s">
         <v>474</v>
       </c>
-      <c r="B117" t="s">
+      <c r="C117" t="s">
         <v>475</v>
       </c>
-      <c r="C117" t="s">
+      <c r="D117" t="s">
+        <v>9</v>
+      </c>
+      <c r="E117" t="s">
         <v>476</v>
       </c>
-      <c r="D117" t="s">
-        <v>9</v>
-      </c>
-      <c r="E117" t="s">
+    </row>
+    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
         <v>477</v>
       </c>
-    </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A118" t="s">
+      <c r="B118" t="s">
         <v>478</v>
       </c>
-      <c r="B118" t="s">
+      <c r="C118" t="s">
         <v>479</v>
       </c>
-      <c r="C118" t="s">
+      <c r="D118" t="s">
+        <v>9</v>
+      </c>
+      <c r="E118" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
         <v>480</v>
       </c>
-      <c r="D118" t="s">
-        <v>9</v>
-      </c>
-      <c r="E118" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A119" t="s">
+      <c r="B119" t="s">
         <v>481</v>
       </c>
-      <c r="B119" t="s">
+      <c r="C119" t="s">
         <v>482</v>
-      </c>
-      <c r="C119" t="s">
-        <v>483</v>
       </c>
       <c r="D119" t="s">
         <v>26</v>
       </c>
       <c r="E119" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
         <v>484</v>
       </c>
-    </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A120" t="s">
+      <c r="B120" t="s">
         <v>485</v>
       </c>
-      <c r="B120" t="s">
+      <c r="C120" t="s">
         <v>486</v>
       </c>
-      <c r="C120" t="s">
+      <c r="D120" t="s">
+        <v>9</v>
+      </c>
+      <c r="E120" t="s">
         <v>487</v>
       </c>
-      <c r="D120" t="s">
-        <v>9</v>
-      </c>
-      <c r="E120" t="s">
+    </row>
+    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
         <v>488</v>
       </c>
-    </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A121" t="s">
+      <c r="B121" t="s">
         <v>489</v>
       </c>
-      <c r="B121" t="s">
+      <c r="C121" t="s">
         <v>490</v>
       </c>
-      <c r="C121" t="s">
+      <c r="D121" t="s">
+        <v>9</v>
+      </c>
+      <c r="E121" t="s">
         <v>491</v>
       </c>
-      <c r="D121" t="s">
-        <v>9</v>
-      </c>
-      <c r="E121" t="s">
+    </row>
+    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
         <v>492</v>
       </c>
-    </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A122" t="s">
+      <c r="B122" t="s">
         <v>493</v>
       </c>
-      <c r="B122" t="s">
+      <c r="C122" t="s">
         <v>494</v>
       </c>
-      <c r="C122" t="s">
+      <c r="D122" t="s">
+        <v>9</v>
+      </c>
+      <c r="E122" t="s">
         <v>495</v>
       </c>
-      <c r="D122" t="s">
-        <v>9</v>
-      </c>
-      <c r="E122" t="s">
+    </row>
+    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
         <v>496</v>
       </c>
-    </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A123" t="s">
+      <c r="B123" t="s">
         <v>497</v>
       </c>
-      <c r="B123" t="s">
+      <c r="C123" t="s">
         <v>498</v>
       </c>
-      <c r="C123" t="s">
+      <c r="D123" t="s">
+        <v>9</v>
+      </c>
+      <c r="E123" t="s">
         <v>499</v>
       </c>
-      <c r="D123" t="s">
-        <v>9</v>
-      </c>
-      <c r="E123" t="s">
+    </row>
+    <row r="124" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A124" s="4" t="s">
         <v>500</v>
       </c>
-    </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A124" t="s">
+      <c r="B124" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="C124" s="4" t="s">
         <v>501</v>
       </c>
-      <c r="B124" t="s">
-        <v>292</v>
-      </c>
-      <c r="C124" t="s">
+      <c r="D124" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E124" s="4" t="s">
         <v>502</v>
       </c>
-      <c r="D124" t="s">
-        <v>9</v>
-      </c>
-      <c r="E124" t="s">
+      <c r="F124" s="4" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
         <v>503</v>
       </c>
-    </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A125" t="s">
+      <c r="B125" t="s">
         <v>504</v>
       </c>
-      <c r="B125" t="s">
+      <c r="C125" t="s">
         <v>505</v>
       </c>
-      <c r="C125" t="s">
+      <c r="D125" t="s">
+        <v>9</v>
+      </c>
+      <c r="E125" t="s">
         <v>506</v>
       </c>
-      <c r="D125" t="s">
-        <v>9</v>
-      </c>
-      <c r="E125" t="s">
+    </row>
+    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
         <v>507</v>
       </c>
-    </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A126" t="s">
+      <c r="B126" t="s">
         <v>508</v>
       </c>
-      <c r="B126" t="s">
+      <c r="C126" t="s">
         <v>509</v>
       </c>
-      <c r="C126" t="s">
+      <c r="D126" t="s">
+        <v>9</v>
+      </c>
+      <c r="E126" t="s">
         <v>510</v>
       </c>
-      <c r="D126" t="s">
-        <v>9</v>
-      </c>
-      <c r="E126" t="s">
+    </row>
+    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
         <v>511</v>
       </c>
-    </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A127" t="s">
+      <c r="B127" t="s">
         <v>512</v>
       </c>
-      <c r="B127" t="s">
+      <c r="C127" t="s">
         <v>513</v>
       </c>
-      <c r="C127" t="s">
+      <c r="D127" t="s">
+        <v>9</v>
+      </c>
+      <c r="E127" t="s">
         <v>514</v>
       </c>
-      <c r="D127" t="s">
-        <v>9</v>
-      </c>
-      <c r="E127" t="s">
+    </row>
+    <row r="128" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A128" s="2" t="s">
         <v>515</v>
       </c>
-    </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A128" t="s">
+      <c r="B128" s="2" t="s">
         <v>516</v>
       </c>
-      <c r="B128" t="s">
+      <c r="C128" s="2" t="s">
         <v>517</v>
       </c>
-      <c r="C128" t="s">
+      <c r="D128" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E128" s="2" t="s">
         <v>518</v>
       </c>
-      <c r="D128" t="s">
-        <v>9</v>
-      </c>
-      <c r="E128" t="s">
+      <c r="F128" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="G128" s="2">
+        <v>1122</v>
+      </c>
+      <c r="H128" s="2" t="s">
+        <v>969</v>
+      </c>
+      <c r="I128" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="J128" s="2" t="s">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A129" s="4" t="s">
         <v>519</v>
       </c>
-    </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A129" t="s">
+      <c r="B129" s="4" t="s">
         <v>520</v>
       </c>
-      <c r="B129" t="s">
+      <c r="C129" s="4" t="s">
         <v>521</v>
       </c>
-      <c r="C129" t="s">
+      <c r="D129" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E129" s="4" t="s">
+        <v>520</v>
+      </c>
+      <c r="F129" s="4" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A130" s="2" t="s">
         <v>522</v>
       </c>
-      <c r="D129" t="s">
-        <v>9</v>
-      </c>
-      <c r="E129" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A130" t="s">
+      <c r="B130" s="2" t="s">
         <v>523</v>
       </c>
-      <c r="B130" t="s">
+      <c r="C130" s="2" t="s">
         <v>524</v>
       </c>
-      <c r="C130" t="s">
+      <c r="D130" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E130" s="2" t="s">
         <v>525</v>
       </c>
-      <c r="D130" t="s">
-        <v>9</v>
-      </c>
-      <c r="E130" t="s">
+      <c r="F130" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="G130" s="2" t="s">
+        <v>1007</v>
+      </c>
+      <c r="H130" s="2" t="s">
+        <v>969</v>
+      </c>
+      <c r="I130" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="J130" s="2" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
         <v>526</v>
       </c>
-    </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A131" t="s">
+      <c r="B131" t="s">
         <v>527</v>
       </c>
-      <c r="B131" t="s">
+      <c r="C131" t="s">
         <v>528</v>
       </c>
-      <c r="C131" t="s">
+      <c r="D131" t="s">
+        <v>9</v>
+      </c>
+      <c r="E131" t="s">
         <v>529</v>
       </c>
-      <c r="D131" t="s">
-        <v>9</v>
-      </c>
-      <c r="E131" t="s">
+    </row>
+    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
         <v>530</v>
       </c>
-    </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A132" t="s">
+      <c r="B132" t="s">
         <v>531</v>
       </c>
-      <c r="B132" t="s">
+      <c r="C132" t="s">
         <v>532</v>
       </c>
-      <c r="C132" t="s">
+      <c r="D132" t="s">
+        <v>9</v>
+      </c>
+      <c r="E132" t="s">
         <v>533</v>
       </c>
-      <c r="D132" t="s">
-        <v>9</v>
-      </c>
-      <c r="E132" t="s">
+    </row>
+    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
         <v>534</v>
       </c>
-    </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A133" t="s">
+      <c r="B133" t="s">
         <v>535</v>
       </c>
-      <c r="B133" t="s">
+      <c r="C133" t="s">
         <v>536</v>
       </c>
-      <c r="C133" t="s">
+      <c r="D133" t="s">
+        <v>9</v>
+      </c>
+      <c r="E133" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A134" s="2" t="s">
         <v>537</v>
       </c>
-      <c r="D133" t="s">
-        <v>9</v>
-      </c>
-      <c r="E133" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A134" t="s">
+      <c r="B134" s="2" t="s">
         <v>538</v>
       </c>
-      <c r="B134" t="s">
+      <c r="C134" s="2" t="s">
         <v>539</v>
       </c>
-      <c r="C134" t="s">
+      <c r="D134" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E134" s="2" t="s">
         <v>540</v>
       </c>
-      <c r="D134" t="s">
-        <v>9</v>
-      </c>
-      <c r="E134" t="s">
+      <c r="F134" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="G134" s="2">
+        <v>1313</v>
+      </c>
+      <c r="H134" s="2" t="s">
+        <v>969</v>
+      </c>
+      <c r="I134" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="J134" s="2" t="s">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
         <v>541</v>
       </c>
-    </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A135" t="s">
+      <c r="B135" t="s">
         <v>542</v>
       </c>
-      <c r="B135" t="s">
+      <c r="C135" t="s">
         <v>543</v>
       </c>
-      <c r="C135" t="s">
+      <c r="D135" t="s">
+        <v>9</v>
+      </c>
+      <c r="E135" t="s">
         <v>544</v>
       </c>
-      <c r="D135" t="s">
-        <v>9</v>
-      </c>
-      <c r="E135" t="s">
+    </row>
+    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
         <v>545</v>
       </c>
-    </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A136" t="s">
+      <c r="B136" t="s">
         <v>546</v>
       </c>
-      <c r="B136" t="s">
+      <c r="C136" t="s">
         <v>547</v>
       </c>
-      <c r="C136" t="s">
+      <c r="D136" t="s">
+        <v>9</v>
+      </c>
+      <c r="E136" t="s">
         <v>548</v>
       </c>
-      <c r="D136" t="s">
-        <v>9</v>
-      </c>
-      <c r="E136" t="s">
+    </row>
+    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
         <v>549</v>
       </c>
-    </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A137" t="s">
+      <c r="B137" t="s">
         <v>550</v>
       </c>
-      <c r="B137" t="s">
+      <c r="C137" t="s">
         <v>551</v>
       </c>
-      <c r="C137" t="s">
+      <c r="D137" t="s">
+        <v>9</v>
+      </c>
+      <c r="E137" t="s">
         <v>552</v>
       </c>
-      <c r="D137" t="s">
-        <v>9</v>
-      </c>
-      <c r="E137" t="s">
+    </row>
+    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
         <v>553</v>
       </c>
-    </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A138" t="s">
+      <c r="B138" t="s">
         <v>554</v>
       </c>
-      <c r="B138" t="s">
+      <c r="C138" t="s">
         <v>555</v>
       </c>
-      <c r="C138" t="s">
+      <c r="D138" t="s">
+        <v>9</v>
+      </c>
+      <c r="E138" t="s">
         <v>556</v>
       </c>
-      <c r="D138" t="s">
-        <v>9</v>
-      </c>
-      <c r="E138" t="s">
+    </row>
+    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
         <v>557</v>
       </c>
-    </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A139" t="s">
+      <c r="B139" t="s">
         <v>558</v>
       </c>
-      <c r="B139" t="s">
+      <c r="C139" t="s">
         <v>559</v>
       </c>
-      <c r="C139" t="s">
+      <c r="D139" t="s">
+        <v>9</v>
+      </c>
+      <c r="E139" t="s">
         <v>560</v>
       </c>
-      <c r="D139" t="s">
-        <v>9</v>
-      </c>
-      <c r="E139" t="s">
+    </row>
+    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
         <v>561</v>
       </c>
-    </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A140" t="s">
+      <c r="B140" t="s">
         <v>562</v>
       </c>
-      <c r="B140" t="s">
+      <c r="C140" t="s">
         <v>563</v>
       </c>
-      <c r="C140" t="s">
+      <c r="D140" t="s">
+        <v>9</v>
+      </c>
+      <c r="E140" t="s">
         <v>564</v>
       </c>
-      <c r="D140" t="s">
-        <v>9</v>
-      </c>
-      <c r="E140" t="s">
+    </row>
+    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
         <v>565</v>
       </c>
-    </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A141" t="s">
+      <c r="B141" t="s">
         <v>566</v>
       </c>
-      <c r="B141" t="s">
+      <c r="C141" t="s">
         <v>567</v>
       </c>
-      <c r="C141" t="s">
+      <c r="D141" t="s">
+        <v>9</v>
+      </c>
+      <c r="E141" t="s">
         <v>568</v>
       </c>
-      <c r="D141" t="s">
-        <v>9</v>
-      </c>
-      <c r="E141" t="s">
+    </row>
+    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
         <v>569</v>
       </c>
-    </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A142" t="s">
+      <c r="B142" t="s">
         <v>570</v>
       </c>
-      <c r="B142" t="s">
+      <c r="C142" t="s">
         <v>571</v>
-      </c>
-      <c r="C142" t="s">
-        <v>572</v>
       </c>
       <c r="D142" t="s">
         <v>376</v>
       </c>
       <c r="E142" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
+        <v>572</v>
+      </c>
+      <c r="B143" t="s">
         <v>573</v>
       </c>
-      <c r="B143" t="s">
+      <c r="C143" t="s">
         <v>574</v>
       </c>
-      <c r="C143" t="s">
+      <c r="D143" t="s">
         <v>575</v>
       </c>
-      <c r="D143" t="s">
+      <c r="E143" t="s">
         <v>576</v>
       </c>
-      <c r="E143" t="s">
+    </row>
+    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
         <v>577</v>
       </c>
-    </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A144" t="s">
+      <c r="B144" t="s">
         <v>578</v>
       </c>
-      <c r="B144" t="s">
+      <c r="C144" t="s">
         <v>579</v>
-      </c>
-      <c r="C144" t="s">
-        <v>580</v>
       </c>
       <c r="D144" t="s">
         <v>111</v>
       </c>
       <c r="E144" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
         <v>581</v>
       </c>
-    </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A145" t="s">
+      <c r="B145" t="s">
         <v>582</v>
       </c>
-      <c r="B145" t="s">
+      <c r="C145" t="s">
         <v>583</v>
       </c>
-      <c r="C145" t="s">
+      <c r="D145" t="s">
+        <v>9</v>
+      </c>
+      <c r="E145" t="s">
         <v>584</v>
       </c>
-      <c r="D145" t="s">
-        <v>9</v>
-      </c>
-      <c r="E145" t="s">
+    </row>
+    <row r="146" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
         <v>585</v>
       </c>
-    </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A146" t="s">
+      <c r="B146" t="s">
         <v>586</v>
       </c>
-      <c r="B146" t="s">
+      <c r="C146" t="s">
         <v>587</v>
-      </c>
-      <c r="C146" t="s">
-        <v>588</v>
       </c>
       <c r="D146" t="s">
         <v>26</v>
       </c>
       <c r="E146" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="147" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
         <v>589</v>
       </c>
-    </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A147" t="s">
+      <c r="B147" t="s">
         <v>590</v>
       </c>
-      <c r="B147" t="s">
+      <c r="C147" t="s">
         <v>591</v>
       </c>
-      <c r="C147" t="s">
+      <c r="D147" t="s">
+        <v>9</v>
+      </c>
+      <c r="E147" t="s">
         <v>592</v>
       </c>
-      <c r="D147" t="s">
-        <v>9</v>
-      </c>
-      <c r="E147" t="s">
+    </row>
+    <row r="148" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
         <v>593</v>
       </c>
-    </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A148" t="s">
+      <c r="B148" t="s">
         <v>594</v>
       </c>
-      <c r="B148" t="s">
+      <c r="C148" t="s">
         <v>595</v>
       </c>
-      <c r="C148" t="s">
+      <c r="D148" t="s">
+        <v>9</v>
+      </c>
+      <c r="E148" t="s">
         <v>596</v>
       </c>
-      <c r="D148" t="s">
-        <v>9</v>
-      </c>
-      <c r="E148" t="s">
+    </row>
+    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
         <v>597</v>
       </c>
-    </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A149" t="s">
+      <c r="B149" t="s">
         <v>598</v>
       </c>
-      <c r="B149" t="s">
+      <c r="C149" t="s">
         <v>599</v>
       </c>
-      <c r="C149" t="s">
+      <c r="D149" t="s">
+        <v>9</v>
+      </c>
+      <c r="E149" t="s">
         <v>600</v>
       </c>
-      <c r="D149" t="s">
-        <v>9</v>
-      </c>
-      <c r="E149" t="s">
+    </row>
+    <row r="150" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
         <v>601</v>
       </c>
-    </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A150" t="s">
+      <c r="B150" t="s">
         <v>602</v>
       </c>
-      <c r="B150" t="s">
+      <c r="C150" t="s">
         <v>603</v>
       </c>
-      <c r="C150" t="s">
+      <c r="D150" t="s">
+        <v>9</v>
+      </c>
+      <c r="E150" t="s">
         <v>604</v>
       </c>
-      <c r="D150" t="s">
-        <v>9</v>
-      </c>
-      <c r="E150" t="s">
+    </row>
+    <row r="151" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
         <v>605</v>
       </c>
-    </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A151" t="s">
+      <c r="B151" t="s">
+        <v>607</v>
+      </c>
+      <c r="C151" t="s">
+        <v>608</v>
+      </c>
+      <c r="D151" t="s">
+        <v>9</v>
+      </c>
+      <c r="E151" t="s">
         <v>606</v>
       </c>
-      <c r="B151" t="s">
-        <v>608</v>
-      </c>
-      <c r="C151" t="s">
+    </row>
+    <row r="152" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
         <v>609</v>
       </c>
-      <c r="D151" t="s">
-        <v>9</v>
-      </c>
-      <c r="E151" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A152" t="s">
+      <c r="B152" t="s">
         <v>610</v>
       </c>
-      <c r="B152" t="s">
+      <c r="C152" t="s">
         <v>611</v>
       </c>
-      <c r="C152" t="s">
+      <c r="D152" t="s">
+        <v>9</v>
+      </c>
+      <c r="E152" t="s">
         <v>612</v>
       </c>
-      <c r="D152" t="s">
-        <v>9</v>
-      </c>
-      <c r="E152" t="s">
+    </row>
+    <row r="153" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
         <v>613</v>
       </c>
-    </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A153" t="s">
+      <c r="B153" t="s">
         <v>614</v>
       </c>
-      <c r="B153" t="s">
+      <c r="C153" t="s">
         <v>615</v>
       </c>
-      <c r="C153" t="s">
+      <c r="D153" t="s">
+        <v>9</v>
+      </c>
+      <c r="E153" t="s">
         <v>616</v>
       </c>
-      <c r="D153" t="s">
-        <v>9</v>
-      </c>
-      <c r="E153" t="s">
+    </row>
+    <row r="154" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
         <v>617</v>
       </c>
-    </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A154" t="s">
+      <c r="B154" t="s">
         <v>618</v>
       </c>
-      <c r="B154" t="s">
+      <c r="C154" t="s">
         <v>619</v>
       </c>
-      <c r="C154" t="s">
+      <c r="D154" t="s">
+        <v>9</v>
+      </c>
+      <c r="E154" t="s">
         <v>620</v>
       </c>
-      <c r="D154" t="s">
-        <v>9</v>
-      </c>
-      <c r="E154" t="s">
+    </row>
+    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
         <v>621</v>
       </c>
-    </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A155" t="s">
+      <c r="B155" t="s">
         <v>622</v>
       </c>
-      <c r="B155" t="s">
+      <c r="C155" t="s">
         <v>623</v>
       </c>
-      <c r="C155" t="s">
+      <c r="D155" t="s">
         <v>624</v>
       </c>
-      <c r="D155" t="s">
+      <c r="E155" t="s">
         <v>625</v>
       </c>
-      <c r="E155" t="s">
+    </row>
+    <row r="156" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
         <v>626</v>
       </c>
-    </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A156" t="s">
+      <c r="B156" t="s">
         <v>627</v>
       </c>
-      <c r="B156" t="s">
+      <c r="C156" t="s">
         <v>628</v>
       </c>
-      <c r="C156" t="s">
+      <c r="D156" t="s">
+        <v>9</v>
+      </c>
+      <c r="E156" t="s">
         <v>629</v>
       </c>
-      <c r="D156" t="s">
-        <v>9</v>
-      </c>
-      <c r="E156" t="s">
+    </row>
+    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
         <v>630</v>
       </c>
-    </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A157" t="s">
+      <c r="B157" t="s">
         <v>631</v>
       </c>
-      <c r="B157" t="s">
+      <c r="C157" t="s">
         <v>632</v>
-      </c>
-      <c r="C157" t="s">
-        <v>633</v>
       </c>
       <c r="D157" t="s">
         <v>5</v>
       </c>
       <c r="E157" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
+        <v>633</v>
+      </c>
+      <c r="B158" t="s">
         <v>634</v>
       </c>
-      <c r="B158" t="s">
+      <c r="C158" t="s">
         <v>635</v>
       </c>
-      <c r="C158" t="s">
+      <c r="D158" t="s">
+        <v>9</v>
+      </c>
+      <c r="E158" t="s">
         <v>636</v>
       </c>
-      <c r="D158" t="s">
-        <v>9</v>
-      </c>
-      <c r="E158" t="s">
+    </row>
+    <row r="159" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
         <v>637</v>
       </c>
-    </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A159" t="s">
+      <c r="B159" t="s">
         <v>638</v>
       </c>
-      <c r="B159" t="s">
+      <c r="C159" t="s">
         <v>639</v>
       </c>
-      <c r="C159" t="s">
+      <c r="D159" t="s">
+        <v>9</v>
+      </c>
+      <c r="E159" t="s">
         <v>640</v>
       </c>
-      <c r="D159" t="s">
-        <v>9</v>
-      </c>
-      <c r="E159" t="s">
+    </row>
+    <row r="160" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A160" s="2" t="s">
         <v>641</v>
       </c>
-    </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A160" t="s">
+      <c r="B160" s="2" t="s">
         <v>642</v>
       </c>
-      <c r="B160" t="s">
+      <c r="C160" s="2" t="s">
         <v>643</v>
       </c>
-      <c r="C160" t="s">
+      <c r="D160" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E160" s="2" t="s">
         <v>644</v>
       </c>
-      <c r="D160" t="s">
-        <v>9</v>
-      </c>
-      <c r="E160" t="s">
+      <c r="F160" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="G160" s="2" t="s">
+        <v>991</v>
+      </c>
+      <c r="H160" s="2" t="s">
+        <v>969</v>
+      </c>
+      <c r="I160" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="J160" s="2" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="161" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A161" s="2" t="s">
         <v>645</v>
       </c>
-    </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A161" t="s">
+      <c r="B161" s="2" t="s">
         <v>646</v>
       </c>
-      <c r="B161" t="s">
+      <c r="C161" s="2" t="s">
         <v>647</v>
       </c>
-      <c r="C161" t="s">
+      <c r="D161" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E161" s="2" t="s">
         <v>648</v>
       </c>
-      <c r="D161" t="s">
-        <v>9</v>
-      </c>
-      <c r="E161" t="s">
+      <c r="F161" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="G161" s="2" t="s">
+        <v>1031</v>
+      </c>
+      <c r="H161" s="2" t="s">
+        <v>969</v>
+      </c>
+      <c r="I161" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="J161" s="2" t="s">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="162" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
         <v>649</v>
       </c>
-    </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A162" t="s">
+      <c r="B162" t="s">
         <v>650</v>
       </c>
-      <c r="B162" t="s">
+      <c r="C162" t="s">
         <v>651</v>
       </c>
-      <c r="C162" t="s">
+      <c r="D162" t="s">
+        <v>9</v>
+      </c>
+      <c r="E162" t="s">
         <v>652</v>
       </c>
-      <c r="D162" t="s">
-        <v>9</v>
-      </c>
-      <c r="E162" t="s">
+    </row>
+    <row r="163" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
         <v>653</v>
       </c>
-    </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A163" t="s">
+      <c r="B163" t="s">
         <v>654</v>
       </c>
-      <c r="B163" t="s">
+      <c r="C163" t="s">
         <v>655</v>
       </c>
-      <c r="C163" t="s">
+      <c r="D163" t="s">
+        <v>9</v>
+      </c>
+      <c r="E163" t="s">
         <v>656</v>
       </c>
-      <c r="D163" t="s">
-        <v>9</v>
-      </c>
-      <c r="E163" t="s">
+    </row>
+    <row r="164" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
         <v>657</v>
       </c>
-    </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A164" t="s">
+      <c r="B164" t="s">
         <v>658</v>
       </c>
-      <c r="B164" t="s">
+      <c r="C164" t="s">
         <v>659</v>
-      </c>
-      <c r="C164" t="s">
-        <v>660</v>
       </c>
       <c r="D164" t="s">
         <v>179</v>
       </c>
       <c r="E164" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="165" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
         <v>661</v>
       </c>
-    </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A165" t="s">
+      <c r="B165" t="s">
         <v>662</v>
       </c>
-      <c r="B165" t="s">
+      <c r="C165" t="s">
         <v>663</v>
       </c>
-      <c r="C165" t="s">
+      <c r="D165" t="s">
+        <v>9</v>
+      </c>
+      <c r="E165" t="s">
         <v>664</v>
       </c>
-      <c r="D165" t="s">
-        <v>9</v>
-      </c>
-      <c r="E165" t="s">
+    </row>
+    <row r="166" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
         <v>665</v>
       </c>
-    </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A166" t="s">
+      <c r="B166" t="s">
         <v>666</v>
       </c>
-      <c r="B166" t="s">
+      <c r="C166" t="s">
         <v>667</v>
       </c>
-      <c r="C166" t="s">
+      <c r="D166" t="s">
+        <v>9</v>
+      </c>
+      <c r="E166" t="s">
         <v>668</v>
       </c>
-      <c r="D166" t="s">
-        <v>9</v>
-      </c>
-      <c r="E166" t="s">
+    </row>
+    <row r="167" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
         <v>669</v>
       </c>
-    </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A167" t="s">
+      <c r="B167" t="s">
+        <v>671</v>
+      </c>
+      <c r="C167" t="s">
+        <v>672</v>
+      </c>
+      <c r="D167" t="s">
+        <v>9</v>
+      </c>
+      <c r="E167" t="s">
         <v>670</v>
       </c>
-      <c r="B167" t="s">
-        <v>672</v>
-      </c>
-      <c r="C167" t="s">
+    </row>
+    <row r="168" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
         <v>673</v>
       </c>
-      <c r="D167" t="s">
-        <v>9</v>
-      </c>
-      <c r="E167" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A168" t="s">
+      <c r="B168" t="s">
         <v>674</v>
       </c>
-      <c r="B168" t="s">
+      <c r="C168" t="s">
         <v>675</v>
       </c>
-      <c r="C168" t="s">
+      <c r="D168" t="s">
+        <v>9</v>
+      </c>
+      <c r="E168" t="s">
         <v>676</v>
       </c>
-      <c r="D168" t="s">
-        <v>9</v>
-      </c>
-      <c r="E168" t="s">
+    </row>
+    <row r="169" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
         <v>677</v>
       </c>
-    </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A169" t="s">
+      <c r="B169" t="s">
         <v>678</v>
       </c>
-      <c r="B169" t="s">
+      <c r="C169" t="s">
         <v>679</v>
-      </c>
-      <c r="C169" t="s">
-        <v>680</v>
       </c>
       <c r="D169" t="s">
         <v>111</v>
       </c>
       <c r="E169" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="170" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
         <v>681</v>
       </c>
-    </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A170" t="s">
+      <c r="B170" t="s">
         <v>682</v>
       </c>
-      <c r="B170" t="s">
+      <c r="C170" t="s">
         <v>683</v>
       </c>
-      <c r="C170" t="s">
+      <c r="D170" t="s">
+        <v>9</v>
+      </c>
+      <c r="E170" t="s">
         <v>684</v>
       </c>
-      <c r="D170" t="s">
-        <v>9</v>
-      </c>
-      <c r="E170" t="s">
+    </row>
+    <row r="171" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
         <v>685</v>
       </c>
-    </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A171" t="s">
+      <c r="B171" t="s">
         <v>686</v>
       </c>
-      <c r="B171" t="s">
+      <c r="C171" t="s">
         <v>687</v>
       </c>
-      <c r="C171" t="s">
+      <c r="D171" t="s">
+        <v>9</v>
+      </c>
+      <c r="E171" t="s">
         <v>688</v>
       </c>
-      <c r="D171" t="s">
-        <v>9</v>
-      </c>
-      <c r="E171" t="s">
+    </row>
+    <row r="172" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A172" t="s">
+      <c r="B172" t="s">
         <v>690</v>
       </c>
-      <c r="B172" t="s">
+      <c r="C172" t="s">
         <v>691</v>
       </c>
-      <c r="C172" t="s">
+      <c r="D172" t="s">
+        <v>9</v>
+      </c>
+      <c r="E172" t="s">
         <v>692</v>
       </c>
-      <c r="D172" t="s">
-        <v>9</v>
-      </c>
-      <c r="E172" t="s">
+    </row>
+    <row r="173" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A173" s="2" t="s">
         <v>693</v>
       </c>
-    </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A173" t="s">
+      <c r="B173" s="2" t="s">
         <v>694</v>
       </c>
-      <c r="B173" t="s">
+      <c r="C173" s="2" t="s">
         <v>695</v>
       </c>
-      <c r="C173" t="s">
+      <c r="D173" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E173" s="2" t="s">
         <v>696</v>
       </c>
-      <c r="D173" t="s">
-        <v>9</v>
-      </c>
-      <c r="E173" t="s">
+      <c r="F173" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="G173" s="2" t="s">
+        <v>1004</v>
+      </c>
+      <c r="H173" s="2" t="s">
+        <v>969</v>
+      </c>
+      <c r="I173" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="J173" s="2" t="s">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="174" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
         <v>697</v>
       </c>
-    </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A174" t="s">
+      <c r="B174" t="s">
         <v>698</v>
       </c>
-      <c r="B174" t="s">
+      <c r="C174" t="s">
         <v>699</v>
-      </c>
-      <c r="C174" t="s">
-        <v>700</v>
       </c>
       <c r="D174" t="s">
         <v>111</v>
       </c>
       <c r="E174" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="175" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
         <v>701</v>
       </c>
-    </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A175" t="s">
+      <c r="B175" t="s">
         <v>702</v>
       </c>
-      <c r="B175" t="s">
+      <c r="C175" t="s">
         <v>703</v>
-      </c>
-      <c r="C175" t="s">
-        <v>704</v>
       </c>
       <c r="D175" t="s">
         <v>26</v>
       </c>
       <c r="E175" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="176" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
         <v>705</v>
       </c>
-    </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A176" t="s">
+      <c r="B176" t="s">
         <v>706</v>
       </c>
-      <c r="B176" t="s">
+      <c r="C176" t="s">
         <v>707</v>
       </c>
-      <c r="C176" t="s">
+      <c r="D176" t="s">
+        <v>575</v>
+      </c>
+      <c r="E176" t="s">
         <v>708</v>
       </c>
-      <c r="D176" t="s">
-        <v>576</v>
-      </c>
-      <c r="E176" t="s">
+    </row>
+    <row r="177" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A177" s="3" t="s">
         <v>709</v>
       </c>
-    </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A177" t="s">
+      <c r="B177" s="3" t="s">
         <v>710</v>
       </c>
-      <c r="B177" t="s">
+      <c r="C177" s="3" t="s">
         <v>711</v>
       </c>
-      <c r="C177" t="s">
+      <c r="D177" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E177" s="3" t="s">
         <v>712</v>
       </c>
-      <c r="D177" t="s">
-        <v>9</v>
-      </c>
-      <c r="E177" t="s">
+      <c r="F177" s="3" t="s">
+        <v>968</v>
+      </c>
+      <c r="G177" s="3" t="s">
+        <v>969</v>
+      </c>
+      <c r="H177" s="3" t="s">
+        <v>968</v>
+      </c>
+      <c r="I177" s="3" t="s">
+        <v>968</v>
+      </c>
+      <c r="J177" s="3" t="s">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="178" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
         <v>713</v>
       </c>
-      <c r="F177" t="s">
-        <v>970</v>
-      </c>
-      <c r="G177" t="s">
-        <v>970</v>
-      </c>
-    </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A178" t="s">
+      <c r="B178" t="s">
         <v>714</v>
       </c>
-      <c r="B178" t="s">
+      <c r="C178" t="s">
         <v>715</v>
       </c>
-      <c r="C178" t="s">
+      <c r="D178" t="s">
+        <v>9</v>
+      </c>
+      <c r="E178" t="s">
         <v>716</v>
       </c>
-      <c r="D178" t="s">
-        <v>9</v>
-      </c>
-      <c r="E178" t="s">
+    </row>
+    <row r="179" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
         <v>717</v>
       </c>
-    </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A179" t="s">
+      <c r="B179" t="s">
         <v>718</v>
       </c>
-      <c r="B179" t="s">
+      <c r="C179" t="s">
         <v>719</v>
       </c>
-      <c r="C179" t="s">
+      <c r="D179" t="s">
+        <v>9</v>
+      </c>
+      <c r="E179" t="s">
         <v>720</v>
       </c>
-      <c r="D179" t="s">
-        <v>9</v>
-      </c>
-      <c r="E179" t="s">
+    </row>
+    <row r="180" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
         <v>721</v>
       </c>
-    </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A180" t="s">
+      <c r="B180" t="s">
         <v>722</v>
       </c>
-      <c r="B180" t="s">
+      <c r="C180" t="s">
         <v>723</v>
       </c>
-      <c r="C180" t="s">
+      <c r="D180" t="s">
+        <v>9</v>
+      </c>
+      <c r="E180" t="s">
         <v>724</v>
       </c>
-      <c r="D180" t="s">
-        <v>9</v>
-      </c>
-      <c r="E180" t="s">
+    </row>
+    <row r="181" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
         <v>725</v>
       </c>
-    </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A181" t="s">
+      <c r="B181" t="s">
         <v>726</v>
       </c>
-      <c r="B181" t="s">
+      <c r="C181" t="s">
         <v>727</v>
-      </c>
-      <c r="C181" t="s">
-        <v>728</v>
       </c>
       <c r="D181" t="s">
         <v>111</v>
       </c>
       <c r="E181" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="182" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A182" s="2" t="s">
         <v>729</v>
       </c>
-    </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A182" t="s">
+      <c r="B182" s="2" t="s">
         <v>730</v>
       </c>
-      <c r="B182" t="s">
+      <c r="C182" s="2" t="s">
         <v>731</v>
       </c>
-      <c r="C182" t="s">
+      <c r="D182" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E182" s="2" t="s">
         <v>732</v>
       </c>
-      <c r="D182" t="s">
-        <v>9</v>
-      </c>
-      <c r="E182" t="s">
+      <c r="F182" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="G182" s="2" t="s">
+        <v>1020</v>
+      </c>
+      <c r="H182" s="2" t="s">
+        <v>969</v>
+      </c>
+      <c r="I182" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="J182" s="2" t="s">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="183" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
         <v>733</v>
       </c>
-    </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A183" t="s">
+      <c r="B183" t="s">
         <v>734</v>
       </c>
-      <c r="B183" t="s">
+      <c r="C183" t="s">
         <v>735</v>
       </c>
-      <c r="C183" t="s">
+      <c r="D183" t="s">
+        <v>9</v>
+      </c>
+      <c r="E183" t="s">
         <v>736</v>
       </c>
-      <c r="D183" t="s">
-        <v>9</v>
-      </c>
-      <c r="E183" t="s">
+    </row>
+    <row r="184" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
         <v>737</v>
       </c>
-    </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A184" t="s">
+      <c r="B184" t="s">
         <v>738</v>
       </c>
-      <c r="B184" t="s">
+      <c r="C184" t="s">
         <v>739</v>
       </c>
-      <c r="C184" t="s">
+      <c r="D184" t="s">
+        <v>9</v>
+      </c>
+      <c r="E184" t="s">
         <v>740</v>
       </c>
-      <c r="D184" t="s">
-        <v>9</v>
-      </c>
-      <c r="E184" t="s">
+    </row>
+    <row r="185" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
         <v>741</v>
       </c>
-    </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A185" t="s">
+      <c r="B185" t="s">
         <v>742</v>
       </c>
-      <c r="B185" t="s">
+      <c r="C185" t="s">
         <v>743</v>
       </c>
-      <c r="C185" t="s">
+      <c r="D185" t="s">
+        <v>9</v>
+      </c>
+      <c r="E185" t="s">
         <v>744</v>
       </c>
-      <c r="D185" t="s">
-        <v>9</v>
-      </c>
-      <c r="E185" t="s">
+    </row>
+    <row r="186" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
         <v>745</v>
       </c>
-    </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A186" t="s">
+      <c r="B186" t="s">
         <v>746</v>
       </c>
-      <c r="B186" t="s">
+      <c r="C186" t="s">
         <v>747</v>
       </c>
-      <c r="C186" t="s">
+      <c r="D186" t="s">
+        <v>9</v>
+      </c>
+      <c r="E186" t="s">
         <v>748</v>
       </c>
-      <c r="D186" t="s">
-        <v>9</v>
-      </c>
-      <c r="E186" t="s">
+    </row>
+    <row r="187" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
         <v>749</v>
       </c>
-    </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A187" t="s">
+      <c r="B187" t="s">
         <v>750</v>
       </c>
-      <c r="B187" t="s">
+      <c r="C187" t="s">
         <v>751</v>
       </c>
-      <c r="C187" t="s">
+      <c r="D187" t="s">
+        <v>9</v>
+      </c>
+      <c r="E187" t="s">
         <v>752</v>
       </c>
-      <c r="D187" t="s">
-        <v>9</v>
-      </c>
-      <c r="E187" t="s">
+    </row>
+    <row r="188" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
         <v>753</v>
       </c>
-    </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A188" t="s">
+      <c r="B188" t="s">
         <v>754</v>
       </c>
-      <c r="B188" t="s">
+      <c r="C188" t="s">
         <v>755</v>
       </c>
-      <c r="C188" t="s">
+      <c r="D188" t="s">
+        <v>9</v>
+      </c>
+      <c r="E188" t="s">
         <v>756</v>
       </c>
-      <c r="D188" t="s">
-        <v>9</v>
-      </c>
-      <c r="E188" t="s">
+    </row>
+    <row r="189" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
         <v>757</v>
       </c>
-    </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A189" t="s">
+      <c r="B189" t="s">
         <v>758</v>
       </c>
-      <c r="B189" t="s">
+      <c r="C189" t="s">
         <v>759</v>
       </c>
-      <c r="C189" t="s">
+      <c r="D189" t="s">
+        <v>9</v>
+      </c>
+      <c r="E189" t="s">
         <v>760</v>
       </c>
-      <c r="D189" t="s">
-        <v>9</v>
-      </c>
-      <c r="E189" t="s">
+    </row>
+    <row r="190" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A190" s="2" t="s">
         <v>761</v>
       </c>
-    </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A190" t="s">
+      <c r="B190" s="2" t="s">
         <v>762</v>
       </c>
-      <c r="B190" t="s">
+      <c r="C190" s="2" t="s">
         <v>763</v>
       </c>
-      <c r="C190" t="s">
+      <c r="D190" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E190" s="2" t="s">
         <v>764</v>
       </c>
-      <c r="D190" t="s">
-        <v>9</v>
-      </c>
-      <c r="E190" t="s">
+      <c r="F190" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="G190" s="2" t="s">
+        <v>969</v>
+      </c>
+      <c r="H190" s="2" t="s">
+        <v>969</v>
+      </c>
+      <c r="I190" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="J190" s="2" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="191" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
         <v>765</v>
       </c>
-    </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A191" t="s">
+      <c r="B191" t="s">
         <v>766</v>
       </c>
-      <c r="B191" t="s">
+      <c r="C191" t="s">
         <v>767</v>
       </c>
-      <c r="C191" t="s">
+      <c r="D191" t="s">
+        <v>9</v>
+      </c>
+      <c r="E191" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="192" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
         <v>768</v>
       </c>
-      <c r="D191" t="s">
-        <v>9</v>
-      </c>
-      <c r="E191" t="s">
-        <v>767</v>
-      </c>
-    </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A192" t="s">
+      <c r="B192" t="s">
         <v>769</v>
       </c>
-      <c r="B192" t="s">
+      <c r="C192" t="s">
         <v>770</v>
-      </c>
-      <c r="C192" t="s">
-        <v>771</v>
       </c>
       <c r="D192" t="s">
         <v>26</v>
       </c>
       <c r="E192" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="193" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A193" s="2" t="s">
         <v>772</v>
       </c>
-    </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A193" t="s">
+      <c r="B193" s="2" t="s">
         <v>773</v>
       </c>
-      <c r="B193" t="s">
+      <c r="C193" s="2" t="s">
         <v>774</v>
       </c>
-      <c r="C193" t="s">
+      <c r="D193" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E193" s="2" t="s">
         <v>775</v>
       </c>
-      <c r="D193" t="s">
-        <v>9</v>
-      </c>
-      <c r="E193" t="s">
+      <c r="F193" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="G193" s="2" t="s">
+        <v>969</v>
+      </c>
+      <c r="H193" s="2" t="s">
+        <v>969</v>
+      </c>
+      <c r="I193" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="J193" s="2" t="s">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="194" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
         <v>776</v>
       </c>
-    </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A194" t="s">
+      <c r="B194" t="s">
         <v>777</v>
       </c>
-      <c r="B194" t="s">
+      <c r="C194" t="s">
         <v>778</v>
-      </c>
-      <c r="C194" t="s">
-        <v>779</v>
       </c>
       <c r="D194" t="s">
         <v>136</v>
       </c>
       <c r="E194" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="195" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A195" s="2" t="s">
         <v>780</v>
       </c>
-    </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A195" t="s">
+      <c r="B195" s="2" t="s">
         <v>781</v>
       </c>
-      <c r="B195" t="s">
+      <c r="C195" s="2" t="s">
         <v>782</v>
       </c>
-      <c r="C195" t="s">
+      <c r="D195" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E195" s="2" t="s">
         <v>783</v>
       </c>
-      <c r="D195" t="s">
-        <v>9</v>
-      </c>
-      <c r="E195" t="s">
+      <c r="F195" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="G195" s="2" t="s">
+        <v>1018</v>
+      </c>
+      <c r="H195" s="2" t="s">
+        <v>969</v>
+      </c>
+      <c r="I195" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="J195" s="2" t="s">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="196" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
         <v>784</v>
       </c>
-    </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A196" t="s">
+      <c r="B196" t="s">
         <v>785</v>
       </c>
-      <c r="B196" t="s">
+      <c r="C196" t="s">
         <v>786</v>
       </c>
-      <c r="C196" t="s">
+      <c r="D196" t="s">
+        <v>9</v>
+      </c>
+      <c r="E196" t="s">
         <v>787</v>
       </c>
-      <c r="D196" t="s">
-        <v>9</v>
-      </c>
-      <c r="E196" t="s">
+    </row>
+    <row r="197" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
         <v>788</v>
       </c>
-    </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A197" t="s">
+      <c r="B197" t="s">
         <v>789</v>
       </c>
-      <c r="B197" t="s">
+      <c r="C197" t="s">
         <v>790</v>
       </c>
-      <c r="C197" t="s">
+      <c r="D197" t="s">
+        <v>9</v>
+      </c>
+      <c r="E197" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="198" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
         <v>791</v>
       </c>
-      <c r="D197" t="s">
-        <v>9</v>
-      </c>
-      <c r="E197" t="s">
-        <v>790</v>
-      </c>
-    </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A198" t="s">
+      <c r="B198" t="s">
         <v>792</v>
       </c>
-      <c r="B198" t="s">
+      <c r="C198" t="s">
         <v>793</v>
       </c>
-      <c r="C198" t="s">
+      <c r="D198" t="s">
+        <v>9</v>
+      </c>
+      <c r="E198" t="s">
         <v>794</v>
       </c>
-      <c r="D198" t="s">
-        <v>9</v>
-      </c>
-      <c r="E198" t="s">
+    </row>
+    <row r="199" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
         <v>795</v>
       </c>
-    </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A199" t="s">
+      <c r="B199" t="s">
         <v>796</v>
       </c>
-      <c r="B199" t="s">
+      <c r="C199" t="s">
         <v>797</v>
       </c>
-      <c r="C199" t="s">
+      <c r="D199" t="s">
+        <v>9</v>
+      </c>
+      <c r="E199" t="s">
         <v>798</v>
       </c>
-      <c r="D199" t="s">
-        <v>9</v>
-      </c>
-      <c r="E199" t="s">
+    </row>
+    <row r="200" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
         <v>799</v>
       </c>
-    </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A200" t="s">
+      <c r="B200" t="s">
         <v>800</v>
       </c>
-      <c r="B200" t="s">
+      <c r="C200" t="s">
         <v>801</v>
       </c>
-      <c r="C200" t="s">
+      <c r="D200" t="s">
+        <v>9</v>
+      </c>
+      <c r="E200" t="s">
         <v>802</v>
       </c>
-      <c r="D200" t="s">
-        <v>9</v>
-      </c>
-      <c r="E200" t="s">
+    </row>
+    <row r="201" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
         <v>803</v>
       </c>
-    </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A201" t="s">
+      <c r="B201" t="s">
         <v>804</v>
       </c>
-      <c r="B201" t="s">
+      <c r="C201" t="s">
         <v>805</v>
       </c>
-      <c r="C201" t="s">
+      <c r="D201" t="s">
+        <v>9</v>
+      </c>
+      <c r="E201" t="s">
         <v>806</v>
       </c>
-      <c r="D201" t="s">
-        <v>9</v>
-      </c>
-      <c r="E201" t="s">
+    </row>
+    <row r="202" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
         <v>807</v>
       </c>
-    </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A202" t="s">
+      <c r="B202" t="s">
         <v>808</v>
       </c>
-      <c r="B202" t="s">
+      <c r="C202" t="s">
         <v>809</v>
       </c>
-      <c r="C202" t="s">
+      <c r="D202" t="s">
+        <v>9</v>
+      </c>
+      <c r="E202" t="s">
         <v>810</v>
       </c>
-      <c r="D202" t="s">
-        <v>9</v>
-      </c>
-      <c r="E202" t="s">
+    </row>
+    <row r="203" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
         <v>811</v>
       </c>
-    </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A203" t="s">
+      <c r="B203" t="s">
         <v>812</v>
       </c>
-      <c r="B203" t="s">
+      <c r="C203" t="s">
         <v>813</v>
       </c>
-      <c r="C203" t="s">
+      <c r="D203" t="s">
+        <v>9</v>
+      </c>
+      <c r="E203" t="s">
         <v>814</v>
       </c>
-      <c r="D203" t="s">
-        <v>9</v>
-      </c>
-      <c r="E203" t="s">
+    </row>
+    <row r="204" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
         <v>815</v>
       </c>
-    </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A204" t="s">
+      <c r="B204" t="s">
         <v>816</v>
       </c>
-      <c r="B204" t="s">
+      <c r="C204" t="s">
         <v>817</v>
-      </c>
-      <c r="C204" t="s">
-        <v>818</v>
       </c>
       <c r="D204" t="s">
         <v>69</v>
       </c>
       <c r="E204" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="205" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
         <v>819</v>
       </c>
-    </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A205" t="s">
+      <c r="B205" t="s">
         <v>820</v>
       </c>
-      <c r="B205" t="s">
+      <c r="C205" t="s">
         <v>821</v>
       </c>
-      <c r="C205" t="s">
+      <c r="D205" t="s">
+        <v>9</v>
+      </c>
+      <c r="E205" t="s">
         <v>822</v>
       </c>
-      <c r="D205" t="s">
-        <v>9</v>
-      </c>
-      <c r="E205" t="s">
+    </row>
+    <row r="206" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
         <v>823</v>
       </c>
-    </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A206" t="s">
+      <c r="B206" t="s">
         <v>824</v>
       </c>
-      <c r="B206" t="s">
+      <c r="C206" t="s">
         <v>825</v>
       </c>
-      <c r="C206" t="s">
+      <c r="D206" t="s">
+        <v>9</v>
+      </c>
+      <c r="E206" t="s">
         <v>826</v>
       </c>
-      <c r="D206" t="s">
-        <v>9</v>
-      </c>
-      <c r="E206" t="s">
+    </row>
+    <row r="207" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
         <v>827</v>
       </c>
-    </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A207" t="s">
+      <c r="B207" t="s">
         <v>828</v>
       </c>
-      <c r="B207" t="s">
+      <c r="C207" t="s">
         <v>829</v>
-      </c>
-      <c r="C207" t="s">
-        <v>830</v>
       </c>
       <c r="D207" t="s">
         <v>26</v>
       </c>
       <c r="E207" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="208" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
         <v>831</v>
       </c>
-    </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A208" t="s">
+      <c r="B208" t="s">
         <v>832</v>
       </c>
-      <c r="B208" t="s">
+      <c r="C208" t="s">
         <v>833</v>
       </c>
-      <c r="C208" t="s">
+      <c r="D208" t="s">
+        <v>9</v>
+      </c>
+      <c r="E208" t="s">
         <v>834</v>
       </c>
-      <c r="D208" t="s">
-        <v>9</v>
-      </c>
-      <c r="E208" t="s">
+    </row>
+    <row r="209" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
         <v>835</v>
       </c>
-    </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A209" t="s">
+      <c r="B209" t="s">
         <v>836</v>
       </c>
-      <c r="B209" t="s">
+      <c r="C209" t="s">
         <v>837</v>
-      </c>
-      <c r="C209" t="s">
-        <v>838</v>
       </c>
       <c r="D209" t="s">
         <v>111</v>
       </c>
       <c r="E209" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="210" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
         <v>839</v>
       </c>
-    </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A210" t="s">
+      <c r="B210" t="s">
         <v>840</v>
       </c>
-      <c r="B210" t="s">
+      <c r="C210" t="s">
         <v>841</v>
       </c>
-      <c r="C210" t="s">
+      <c r="D210" t="s">
+        <v>9</v>
+      </c>
+      <c r="E210" t="s">
         <v>842</v>
       </c>
-      <c r="D210" t="s">
-        <v>9</v>
-      </c>
-      <c r="E210" t="s">
+    </row>
+    <row r="211" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
         <v>843</v>
       </c>
-    </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A211" t="s">
+      <c r="B211" t="s">
         <v>844</v>
       </c>
-      <c r="B211" t="s">
+      <c r="C211" t="s">
         <v>845</v>
       </c>
-      <c r="C211" t="s">
+      <c r="D211" t="s">
+        <v>9</v>
+      </c>
+      <c r="E211" t="s">
         <v>846</v>
       </c>
-      <c r="D211" t="s">
-        <v>9</v>
-      </c>
-      <c r="E211" t="s">
+    </row>
+    <row r="212" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
         <v>847</v>
       </c>
-    </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A212" t="s">
+      <c r="B212" t="s">
         <v>848</v>
       </c>
-      <c r="B212" t="s">
+      <c r="C212" t="s">
         <v>849</v>
       </c>
-      <c r="C212" t="s">
+      <c r="D212" t="s">
+        <v>9</v>
+      </c>
+      <c r="E212" t="s">
         <v>850</v>
       </c>
-      <c r="D212" t="s">
-        <v>9</v>
-      </c>
-      <c r="E212" t="s">
+    </row>
+    <row r="213" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
         <v>851</v>
       </c>
-    </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A213" t="s">
+      <c r="B213" t="s">
         <v>852</v>
       </c>
-      <c r="B213" t="s">
+      <c r="C213" t="s">
         <v>853</v>
       </c>
-      <c r="C213" t="s">
+      <c r="D213" t="s">
         <v>854</v>
       </c>
-      <c r="D213" t="s">
+      <c r="E213" t="s">
         <v>855</v>
       </c>
-      <c r="E213" t="s">
+    </row>
+    <row r="214" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
         <v>856</v>
       </c>
-    </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A214" t="s">
+      <c r="B214" t="s">
         <v>857</v>
       </c>
-      <c r="B214" t="s">
+      <c r="C214" t="s">
         <v>858</v>
       </c>
-      <c r="C214" t="s">
+      <c r="D214" t="s">
+        <v>9</v>
+      </c>
+      <c r="E214" t="s">
         <v>859</v>
       </c>
-      <c r="D214" t="s">
-        <v>9</v>
-      </c>
-      <c r="E214" t="s">
+    </row>
+    <row r="215" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
         <v>860</v>
       </c>
-    </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A215" t="s">
+      <c r="B215" t="s">
         <v>861</v>
       </c>
-      <c r="B215" t="s">
+      <c r="C215" t="s">
         <v>862</v>
       </c>
-      <c r="C215" t="s">
+      <c r="D215" t="s">
+        <v>9</v>
+      </c>
+      <c r="E215" t="s">
         <v>863</v>
       </c>
-      <c r="D215" t="s">
-        <v>9</v>
-      </c>
-      <c r="E215" t="s">
+    </row>
+    <row r="216" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
         <v>864</v>
       </c>
-    </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A216" t="s">
+      <c r="B216" t="s">
         <v>865</v>
       </c>
-      <c r="B216" t="s">
+      <c r="C216" t="s">
         <v>866</v>
       </c>
-      <c r="C216" t="s">
+      <c r="D216" t="s">
+        <v>9</v>
+      </c>
+      <c r="E216" t="s">
         <v>867</v>
       </c>
-      <c r="D216" t="s">
-        <v>9</v>
-      </c>
-      <c r="E216" t="s">
+    </row>
+    <row r="217" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
         <v>868</v>
       </c>
-    </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A217" t="s">
+      <c r="B217" t="s">
         <v>869</v>
       </c>
-      <c r="B217" t="s">
+      <c r="C217" t="s">
         <v>870</v>
       </c>
-      <c r="C217" t="s">
+      <c r="D217" t="s">
+        <v>9</v>
+      </c>
+      <c r="E217" t="s">
         <v>871</v>
       </c>
-      <c r="D217" t="s">
-        <v>9</v>
-      </c>
-      <c r="E217" t="s">
+    </row>
+    <row r="218" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A218" s="2" t="s">
         <v>872</v>
       </c>
-    </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A218" t="s">
+      <c r="B218" s="2" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C218" s="2" t="s">
         <v>873</v>
       </c>
-      <c r="B218" t="s">
+      <c r="D218" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E218" s="2" t="s">
         <v>874</v>
       </c>
-      <c r="C218" t="s">
+      <c r="F218" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="G218" s="2" t="s">
+        <v>969</v>
+      </c>
+      <c r="H218" s="2" t="s">
+        <v>969</v>
+      </c>
+      <c r="I218" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="J218" s="2" t="s">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="219" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
         <v>875</v>
       </c>
-      <c r="D218" t="s">
-        <v>9</v>
-      </c>
-      <c r="E218" t="s">
+      <c r="B219" t="s">
         <v>876</v>
       </c>
-    </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A219" t="s">
+      <c r="C219" t="s">
         <v>877</v>
       </c>
-      <c r="B219" t="s">
+      <c r="D219" t="s">
+        <v>9</v>
+      </c>
+      <c r="E219" t="s">
         <v>878</v>
       </c>
-      <c r="C219" t="s">
+    </row>
+    <row r="220" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
         <v>879</v>
       </c>
-      <c r="D219" t="s">
-        <v>9</v>
-      </c>
-      <c r="E219" t="s">
+      <c r="B220" t="s">
         <v>880</v>
       </c>
-    </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A220" t="s">
+      <c r="C220" t="s">
         <v>881</v>
       </c>
-      <c r="B220" t="s">
+      <c r="D220" t="s">
+        <v>9</v>
+      </c>
+      <c r="E220" t="s">
         <v>882</v>
       </c>
-      <c r="C220" t="s">
+    </row>
+    <row r="221" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
         <v>883</v>
       </c>
-      <c r="D220" t="s">
-        <v>9</v>
-      </c>
-      <c r="E220" t="s">
+      <c r="B221" t="s">
         <v>884</v>
       </c>
-    </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A221" t="s">
+      <c r="C221" t="s">
         <v>885</v>
       </c>
-      <c r="B221" t="s">
+      <c r="D221" t="s">
+        <v>9</v>
+      </c>
+      <c r="E221" t="s">
         <v>886</v>
       </c>
-      <c r="C221" t="s">
+    </row>
+    <row r="222" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A222" s="2" t="s">
         <v>887</v>
       </c>
-      <c r="D221" t="s">
-        <v>9</v>
-      </c>
-      <c r="E221" t="s">
+      <c r="B222" s="2" t="s">
         <v>888</v>
       </c>
-    </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A222" t="s">
+      <c r="C222" s="2" t="s">
         <v>889</v>
       </c>
-      <c r="B222" t="s">
+      <c r="D222" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E222" s="2" t="s">
+        <v>966</v>
+      </c>
+      <c r="F222" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="G222" s="2" t="s">
+        <v>1028</v>
+      </c>
+      <c r="H222" s="2" t="s">
+        <v>969</v>
+      </c>
+      <c r="I222" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="J222" s="2" t="s">
+        <v>1029</v>
+      </c>
+      <c r="K222" s="2">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="223" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
         <v>890</v>
       </c>
-      <c r="C222" t="s">
+      <c r="B223" t="s">
         <v>891</v>
       </c>
-      <c r="D222" t="s">
-        <v>9</v>
-      </c>
-      <c r="E222" t="s">
+      <c r="C223" t="s">
+        <v>892</v>
+      </c>
+      <c r="D223" t="s">
+        <v>9</v>
+      </c>
+      <c r="E223" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="224" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A224" s="2" t="s">
+        <v>894</v>
+      </c>
+      <c r="B224" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="C224" s="2" t="s">
+        <v>895</v>
+      </c>
+      <c r="D224" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E224" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="F224" s="2" t="s">
         <v>968</v>
       </c>
-    </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A223" t="s">
-        <v>892</v>
-      </c>
-      <c r="B223" t="s">
-        <v>893</v>
-      </c>
-      <c r="C223" t="s">
-        <v>894</v>
-      </c>
-      <c r="D223" t="s">
-        <v>9</v>
-      </c>
-      <c r="E223" t="s">
-        <v>895</v>
-      </c>
-    </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A224" t="s">
-        <v>896</v>
-      </c>
-      <c r="B224" t="s">
-        <v>310</v>
-      </c>
-      <c r="C224" t="s">
-        <v>897</v>
-      </c>
-      <c r="D224" t="s">
-        <v>9</v>
-      </c>
-      <c r="E224" t="s">
-        <v>311</v>
+      <c r="G224" s="2" t="s">
+        <v>997</v>
+      </c>
+      <c r="H224" s="2" t="s">
+        <v>969</v>
+      </c>
+      <c r="I224" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="J224" s="2" t="s">
+        <v>998</v>
       </c>
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
+        <v>896</v>
+      </c>
+      <c r="B225" t="s">
+        <v>897</v>
+      </c>
+      <c r="C225" t="s">
         <v>898</v>
       </c>
-      <c r="B225" t="s">
+      <c r="D225" t="s">
+        <v>9</v>
+      </c>
+      <c r="E225" t="s">
         <v>899</v>
-      </c>
-      <c r="C225" t="s">
-        <v>900</v>
-      </c>
-      <c r="D225" t="s">
-        <v>9</v>
-      </c>
-      <c r="E225" t="s">
-        <v>901</v>
       </c>
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
+        <v>900</v>
+      </c>
+      <c r="B226" t="s">
+        <v>901</v>
+      </c>
+      <c r="C226" t="s">
         <v>902</v>
       </c>
-      <c r="B226" t="s">
+      <c r="D226" t="s">
+        <v>9</v>
+      </c>
+      <c r="E226" t="s">
         <v>903</v>
-      </c>
-      <c r="C226" t="s">
-        <v>904</v>
-      </c>
-      <c r="D226" t="s">
-        <v>9</v>
-      </c>
-      <c r="E226" t="s">
-        <v>905</v>
       </c>
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
+        <v>904</v>
+      </c>
+      <c r="B227" t="s">
+        <v>905</v>
+      </c>
+      <c r="C227" t="s">
         <v>906</v>
       </c>
-      <c r="B227" t="s">
+      <c r="D227" t="s">
+        <v>9</v>
+      </c>
+      <c r="E227" t="s">
         <v>907</v>
-      </c>
-      <c r="C227" t="s">
-        <v>908</v>
-      </c>
-      <c r="D227" t="s">
-        <v>9</v>
-      </c>
-      <c r="E227" t="s">
-        <v>909</v>
       </c>
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
+        <v>908</v>
+      </c>
+      <c r="B228" t="s">
+        <v>909</v>
+      </c>
+      <c r="C228" t="s">
         <v>910</v>
       </c>
-      <c r="B228" t="s">
+      <c r="D228" t="s">
         <v>911</v>
       </c>
-      <c r="C228" t="s">
+      <c r="E228" t="s">
         <v>912</v>
-      </c>
-      <c r="D228" t="s">
-        <v>913</v>
-      </c>
-      <c r="E228" t="s">
-        <v>914</v>
       </c>
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
+        <v>913</v>
+      </c>
+      <c r="B229" t="s">
+        <v>914</v>
+      </c>
+      <c r="C229" t="s">
         <v>915</v>
       </c>
-      <c r="B229" t="s">
+      <c r="D229" t="s">
+        <v>9</v>
+      </c>
+      <c r="E229" t="s">
         <v>916</v>
-      </c>
-      <c r="C229" t="s">
-        <v>917</v>
-      </c>
-      <c r="D229" t="s">
-        <v>9</v>
-      </c>
-      <c r="E229" t="s">
-        <v>918</v>
       </c>
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
+        <v>917</v>
+      </c>
+      <c r="B230" t="s">
+        <v>918</v>
+      </c>
+      <c r="C230" t="s">
         <v>919</v>
       </c>
-      <c r="B230" t="s">
+      <c r="D230" t="s">
+        <v>9</v>
+      </c>
+      <c r="E230" t="s">
         <v>920</v>
-      </c>
-      <c r="C230" t="s">
-        <v>921</v>
-      </c>
-      <c r="D230" t="s">
-        <v>9</v>
-      </c>
-      <c r="E230" t="s">
-        <v>922</v>
       </c>
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
+        <v>921</v>
+      </c>
+      <c r="B231" t="s">
+        <v>922</v>
+      </c>
+      <c r="C231" t="s">
         <v>923</v>
-      </c>
-      <c r="B231" t="s">
-        <v>924</v>
-      </c>
-      <c r="C231" t="s">
-        <v>925</v>
       </c>
       <c r="D231" t="s">
         <v>26</v>
       </c>
       <c r="E231" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
+        <v>925</v>
+      </c>
+      <c r="B232" t="s">
+        <v>926</v>
+      </c>
+      <c r="C232" t="s">
         <v>927</v>
-      </c>
-      <c r="B232" t="s">
-        <v>928</v>
-      </c>
-      <c r="C232" t="s">
-        <v>929</v>
       </c>
       <c r="D232" t="s">
         <v>56</v>
       </c>
       <c r="E232" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
+        <v>929</v>
+      </c>
+      <c r="B233" t="s">
+        <v>930</v>
+      </c>
+      <c r="C233" t="s">
         <v>931</v>
       </c>
-      <c r="B233" t="s">
+      <c r="D233" t="s">
+        <v>9</v>
+      </c>
+      <c r="E233" t="s">
         <v>932</v>
-      </c>
-      <c r="C233" t="s">
-        <v>933</v>
-      </c>
-      <c r="D233" t="s">
-        <v>9</v>
-      </c>
-      <c r="E233" t="s">
-        <v>934</v>
       </c>
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
+        <v>933</v>
+      </c>
+      <c r="B234" t="s">
+        <v>934</v>
+      </c>
+      <c r="C234" t="s">
         <v>935</v>
       </c>
-      <c r="B234" t="s">
+      <c r="D234" t="s">
+        <v>9</v>
+      </c>
+      <c r="E234" t="s">
         <v>936</v>
-      </c>
-      <c r="C234" t="s">
-        <v>937</v>
-      </c>
-      <c r="D234" t="s">
-        <v>9</v>
-      </c>
-      <c r="E234" t="s">
-        <v>938</v>
       </c>
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
+        <v>937</v>
+      </c>
+      <c r="B235" t="s">
+        <v>938</v>
+      </c>
+      <c r="C235" t="s">
         <v>939</v>
-      </c>
-      <c r="B235" t="s">
-        <v>940</v>
-      </c>
-      <c r="C235" t="s">
-        <v>941</v>
       </c>
       <c r="D235" t="s">
         <v>111</v>
       </c>
       <c r="E235" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
+        <v>941</v>
+      </c>
+      <c r="B236" t="s">
+        <v>942</v>
+      </c>
+      <c r="C236" t="s">
         <v>943</v>
       </c>
-      <c r="B236" t="s">
+      <c r="D236" t="s">
+        <v>9</v>
+      </c>
+      <c r="E236" t="s">
         <v>944</v>
-      </c>
-      <c r="C236" t="s">
-        <v>945</v>
-      </c>
-      <c r="D236" t="s">
-        <v>9</v>
-      </c>
-      <c r="E236" t="s">
-        <v>946</v>
       </c>
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
+        <v>945</v>
+      </c>
+      <c r="B237" t="s">
+        <v>946</v>
+      </c>
+      <c r="C237" t="s">
         <v>947</v>
       </c>
-      <c r="B237" t="s">
+      <c r="D237" t="s">
+        <v>9</v>
+      </c>
+      <c r="E237" t="s">
         <v>948</v>
-      </c>
-      <c r="C237" t="s">
-        <v>949</v>
-      </c>
-      <c r="D237" t="s">
-        <v>9</v>
-      </c>
-      <c r="E237" t="s">
-        <v>950</v>
       </c>
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
+        <v>949</v>
+      </c>
+      <c r="B238" t="s">
+        <v>950</v>
+      </c>
+      <c r="C238" t="s">
         <v>951</v>
-      </c>
-      <c r="B238" t="s">
-        <v>952</v>
-      </c>
-      <c r="C238" t="s">
-        <v>953</v>
       </c>
       <c r="D238" t="s">
         <v>111</v>
       </c>
       <c r="E238" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
+        <v>953</v>
+      </c>
+      <c r="B239" t="s">
+        <v>954</v>
+      </c>
+      <c r="C239" t="s">
         <v>955</v>
       </c>
-      <c r="B239" t="s">
+      <c r="D239" t="s">
+        <v>9</v>
+      </c>
+      <c r="E239" t="s">
         <v>956</v>
-      </c>
-      <c r="C239" t="s">
-        <v>957</v>
-      </c>
-      <c r="D239" t="s">
-        <v>9</v>
-      </c>
-      <c r="E239" t="s">
-        <v>958</v>
       </c>
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
+        <v>957</v>
+      </c>
+      <c r="B240" t="s">
+        <v>958</v>
+      </c>
+      <c r="C240" t="s">
         <v>959</v>
       </c>
-      <c r="B240" t="s">
+      <c r="D240" t="s">
+        <v>9</v>
+      </c>
+      <c r="E240" t="s">
         <v>960</v>
-      </c>
-      <c r="C240" t="s">
-        <v>961</v>
-      </c>
-      <c r="D240" t="s">
-        <v>9</v>
-      </c>
-      <c r="E240" t="s">
-        <v>962</v>
       </c>
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
+        <v>961</v>
+      </c>
+      <c r="B241" t="s">
+        <v>962</v>
+      </c>
+      <c r="C241" t="s">
         <v>963</v>
       </c>
-      <c r="B241" t="s">
+      <c r="D241" t="s">
+        <v>9</v>
+      </c>
+      <c r="E241" t="s">
         <v>964</v>
-      </c>
-      <c r="C241" t="s">
-        <v>965</v>
-      </c>
-      <c r="D241" t="s">
-        <v>9</v>
-      </c>
-      <c r="E241" t="s">
-        <v>966</v>
       </c>
     </row>
   </sheetData>
